--- a/research/traditional_assets/database/data/south_africa/south_africa_real_estate_development.xlsx
+++ b/research/traditional_assets/database/data/south_africa/south_africa_real_estate_development.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08300753858046889</v>
+        <v>0.08281626822630163</v>
       </c>
       <c r="C2">
-        <v>96.25717839002088</v>
+        <v>95.48448593529349</v>
       </c>
       <c r="D2">
-        <v>86.74717839002088</v>
+        <v>86.89848593529349</v>
       </c>
       <c r="E2">
-        <v>-58.3</v>
+        <v>-57.376</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.924</v>
       </c>
       <c r="G2">
         <v>9.51</v>
@@ -1445,28 +1445,28 @@
         <v>16.875</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0464772</v>
       </c>
       <c r="N2">
-        <v>16.875</v>
+        <v>16.8285228</v>
       </c>
       <c r="O2">
-        <v>4.55625</v>
+        <v>4.543701156</v>
       </c>
       <c r="P2">
-        <v>12.31875</v>
+        <v>12.284821644</v>
       </c>
       <c r="Q2">
-        <v>12.31875</v>
+        <v>12.284821644</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08300753858046889</v>
+        <v>0.08328189719828447</v>
       </c>
       <c r="T2">
-        <v>0.4457367247241993</v>
+        <v>0.4490234702701455</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>363.0812527432805</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08281626822630163</v>
+        <v>0.08262499787213437</v>
       </c>
       <c r="C3">
-        <v>95.48448593529349</v>
+        <v>94.71232223495207</v>
       </c>
       <c r="D3">
-        <v>86.89848593529349</v>
+        <v>87.05032223495206</v>
       </c>
       <c r="E3">
-        <v>-57.376</v>
+        <v>-56.45200000000001</v>
       </c>
       <c r="F3">
-        <v>0.924</v>
+        <v>1.848</v>
       </c>
       <c r="G3">
         <v>9.51</v>
@@ -1527,28 +1527,28 @@
         <v>16.875</v>
       </c>
       <c r="M3">
-        <v>0.0464772</v>
+        <v>0.09295440000000001</v>
       </c>
       <c r="N3">
-        <v>16.8285228</v>
+        <v>16.7820456</v>
       </c>
       <c r="O3">
-        <v>4.543701156</v>
+        <v>4.531152312000001</v>
       </c>
       <c r="P3">
-        <v>12.284821644</v>
+        <v>12.250893288</v>
       </c>
       <c r="Q3">
-        <v>12.284821644</v>
+        <v>12.250893288</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08328189719828447</v>
+        <v>0.08356185497156568</v>
       </c>
       <c r="T3">
-        <v>0.4490234702701455</v>
+        <v>0.4523772922558048</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>363.0812527432805</v>
+        <v>181.5406263716403</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08262499787213437</v>
+        <v>0.08243372751796708</v>
       </c>
       <c r="C4">
-        <v>94.71232223495207</v>
+        <v>93.94069006549952</v>
       </c>
       <c r="D4">
-        <v>87.05032223495206</v>
+        <v>87.20269006549952</v>
       </c>
       <c r="E4">
-        <v>-56.45200000000001</v>
+        <v>-55.52800000000001</v>
       </c>
       <c r="F4">
-        <v>1.848</v>
+        <v>2.772</v>
       </c>
       <c r="G4">
         <v>9.51</v>
@@ -1609,28 +1609,28 @@
         <v>16.875</v>
       </c>
       <c r="M4">
-        <v>0.09295440000000001</v>
+        <v>0.1394316</v>
       </c>
       <c r="N4">
-        <v>16.7820456</v>
+        <v>16.7355684</v>
       </c>
       <c r="O4">
-        <v>4.531152312000001</v>
+        <v>4.518603468</v>
       </c>
       <c r="P4">
-        <v>12.250893288</v>
+        <v>12.216964932</v>
       </c>
       <c r="Q4">
-        <v>12.250893288</v>
+        <v>12.216964932</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08356185497156568</v>
+        <v>0.08384758507006916</v>
       </c>
       <c r="T4">
-        <v>0.4523772922558048</v>
+        <v>0.4558002652102405</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>181.5406263716403</v>
+        <v>121.0270842477602</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08243372751796708</v>
+        <v>0.08224245716379981</v>
       </c>
       <c r="C5">
-        <v>93.94069006549952</v>
+        <v>93.16959222291221</v>
       </c>
       <c r="D5">
-        <v>87.20269006549952</v>
+        <v>87.35559222291221</v>
       </c>
       <c r="E5">
-        <v>-55.52800000000001</v>
+        <v>-54.60400000000001</v>
       </c>
       <c r="F5">
-        <v>2.772</v>
+        <v>3.696</v>
       </c>
       <c r="G5">
         <v>9.51</v>
@@ -1691,28 +1691,28 @@
         <v>16.875</v>
       </c>
       <c r="M5">
-        <v>0.1394316</v>
+        <v>0.1859088</v>
       </c>
       <c r="N5">
-        <v>16.7355684</v>
+        <v>16.6890912</v>
       </c>
       <c r="O5">
-        <v>4.518603468</v>
+        <v>4.506054624</v>
       </c>
       <c r="P5">
-        <v>12.216964932</v>
+        <v>12.183036576</v>
       </c>
       <c r="Q5">
-        <v>12.216964932</v>
+        <v>12.183036576</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08384758507006916</v>
+        <v>0.08413926787895815</v>
       </c>
       <c r="T5">
-        <v>0.4558002652102405</v>
+        <v>0.4592945501012271</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>121.0270842477602</v>
+        <v>90.77031318582014</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08224245716379981</v>
+        <v>0.08205118680963257</v>
       </c>
       <c r="C6">
-        <v>93.16959222291221</v>
+        <v>92.39903152281086</v>
       </c>
       <c r="D6">
-        <v>87.35559222291221</v>
+        <v>87.50903152281086</v>
       </c>
       <c r="E6">
-        <v>-54.60400000000001</v>
+        <v>-53.68000000000001</v>
       </c>
       <c r="F6">
-        <v>3.696</v>
+        <v>4.62</v>
       </c>
       <c r="G6">
         <v>9.51</v>
@@ -1773,28 +1773,28 @@
         <v>16.875</v>
       </c>
       <c r="M6">
-        <v>0.1859088</v>
+        <v>0.232386</v>
       </c>
       <c r="N6">
-        <v>16.6890912</v>
+        <v>16.642614</v>
       </c>
       <c r="O6">
-        <v>4.506054624</v>
+        <v>4.49350578</v>
       </c>
       <c r="P6">
-        <v>12.183036576</v>
+        <v>12.14910822</v>
       </c>
       <c r="Q6">
-        <v>12.183036576</v>
+        <v>12.14910822</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08413926787895815</v>
+        <v>0.08443709137856059</v>
       </c>
       <c r="T6">
-        <v>0.4592945501012271</v>
+        <v>0.4628623988846554</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>90.77031318582014</v>
+        <v>72.61625054865613</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08205118680963257</v>
+        <v>0.08185991645546531</v>
       </c>
       <c r="C7">
-        <v>92.39903152281086</v>
+        <v>91.62901080063358</v>
       </c>
       <c r="D7">
-        <v>87.50903152281086</v>
+        <v>87.66301080063357</v>
       </c>
       <c r="E7">
-        <v>-53.68000000000001</v>
+        <v>-52.756</v>
       </c>
       <c r="F7">
-        <v>4.62</v>
+        <v>5.544</v>
       </c>
       <c r="G7">
         <v>9.51</v>
@@ -1855,28 +1855,28 @@
         <v>16.875</v>
       </c>
       <c r="M7">
-        <v>0.232386</v>
+        <v>0.2788632</v>
       </c>
       <c r="N7">
-        <v>16.642614</v>
+        <v>16.5961368</v>
       </c>
       <c r="O7">
-        <v>4.49350578</v>
+        <v>4.480956936</v>
       </c>
       <c r="P7">
-        <v>12.14910822</v>
+        <v>12.115179864</v>
       </c>
       <c r="Q7">
-        <v>12.14910822</v>
+        <v>12.115179864</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08443709137856059</v>
+        <v>0.08474125154836734</v>
       </c>
       <c r="T7">
-        <v>0.4628623988846554</v>
+        <v>0.466506159344327</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>72.61625054865613</v>
+        <v>60.51354212388009</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08185991645546531</v>
+        <v>0.08166864610129802</v>
       </c>
       <c r="C8">
-        <v>91.62901080063358</v>
+        <v>90.85953291181028</v>
       </c>
       <c r="D8">
-        <v>87.66301080063357</v>
+        <v>87.81753291181028</v>
       </c>
       <c r="E8">
-        <v>-52.756</v>
+        <v>-51.83200000000001</v>
       </c>
       <c r="F8">
-        <v>5.544</v>
+        <v>6.468</v>
       </c>
       <c r="G8">
         <v>9.51</v>
@@ -1937,28 +1937,28 @@
         <v>16.875</v>
       </c>
       <c r="M8">
-        <v>0.2788632</v>
+        <v>0.3253404</v>
       </c>
       <c r="N8">
-        <v>16.5961368</v>
+        <v>16.5496596</v>
       </c>
       <c r="O8">
-        <v>4.480956936</v>
+        <v>4.468408092</v>
       </c>
       <c r="P8">
-        <v>12.115179864</v>
+        <v>12.081251508</v>
       </c>
       <c r="Q8">
-        <v>12.115179864</v>
+        <v>12.081251508</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08474125154836734</v>
+        <v>0.08505195279709465</v>
       </c>
       <c r="T8">
-        <v>0.466506159344327</v>
+        <v>0.4702282802439914</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>60.51354212388009</v>
+        <v>51.86875039189722</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08166864610129802</v>
+        <v>0.08147737574713075</v>
       </c>
       <c r="C9">
-        <v>90.85953291181028</v>
+        <v>90.09060073193935</v>
       </c>
       <c r="D9">
-        <v>87.81753291181028</v>
+        <v>87.97260073193934</v>
       </c>
       <c r="E9">
-        <v>-51.832</v>
+        <v>-50.908</v>
       </c>
       <c r="F9">
-        <v>6.468000000000001</v>
+        <v>7.392</v>
       </c>
       <c r="G9">
         <v>9.51</v>
@@ -2019,28 +2019,28 @@
         <v>16.875</v>
       </c>
       <c r="M9">
-        <v>0.3253404</v>
+        <v>0.3718176</v>
       </c>
       <c r="N9">
-        <v>16.5496596</v>
+        <v>16.5031824</v>
       </c>
       <c r="O9">
-        <v>4.468408092</v>
+        <v>4.455859248</v>
       </c>
       <c r="P9">
-        <v>12.081251508</v>
+        <v>12.047323152</v>
       </c>
       <c r="Q9">
-        <v>12.081251508</v>
+        <v>12.047323152</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08505195279709465</v>
+        <v>0.0853694084207943</v>
       </c>
       <c r="T9">
-        <v>0.4702282802439914</v>
+        <v>0.4740313168153876</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>51.86875039189722</v>
+        <v>45.38515659291007</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08147737574713075</v>
+        <v>0.08128610539296351</v>
       </c>
       <c r="C10">
-        <v>90.09060073193935</v>
+        <v>89.32221715696591</v>
       </c>
       <c r="D10">
-        <v>87.97260073193934</v>
+        <v>88.1282171569659</v>
       </c>
       <c r="E10">
-        <v>-50.908</v>
+        <v>-49.984</v>
       </c>
       <c r="F10">
-        <v>7.392</v>
+        <v>8.316000000000001</v>
       </c>
       <c r="G10">
         <v>9.51</v>
@@ -2101,28 +2101,28 @@
         <v>16.875</v>
       </c>
       <c r="M10">
-        <v>0.3718176</v>
+        <v>0.4182948</v>
       </c>
       <c r="N10">
-        <v>16.5031824</v>
+        <v>16.4567052</v>
       </c>
       <c r="O10">
-        <v>4.455859248</v>
+        <v>4.443310404</v>
       </c>
       <c r="P10">
-        <v>12.047323152</v>
+        <v>12.013394796</v>
       </c>
       <c r="Q10">
-        <v>12.047323152</v>
+        <v>12.013394796</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0853694084207943</v>
+        <v>0.08569384109116868</v>
       </c>
       <c r="T10">
-        <v>0.4740313168153876</v>
+        <v>0.4779179366081333</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>45.38515659291007</v>
+        <v>40.34236141592006</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08128610539296351</v>
+        <v>0.08109483503879623</v>
       </c>
       <c r="C11">
-        <v>89.32221715696591</v>
+        <v>88.55438510336229</v>
       </c>
       <c r="D11">
-        <v>88.1282171569659</v>
+        <v>88.28438510336228</v>
       </c>
       <c r="E11">
-        <v>-49.984</v>
+        <v>-49.06</v>
       </c>
       <c r="F11">
-        <v>8.316000000000001</v>
+        <v>9.24</v>
       </c>
       <c r="G11">
         <v>9.51</v>
@@ -2183,28 +2183,28 @@
         <v>16.875</v>
       </c>
       <c r="M11">
-        <v>0.4182948</v>
+        <v>0.464772</v>
       </c>
       <c r="N11">
-        <v>16.4567052</v>
+        <v>16.410228</v>
       </c>
       <c r="O11">
-        <v>4.443310404</v>
+        <v>4.430761560000001</v>
       </c>
       <c r="P11">
-        <v>12.013394796</v>
+        <v>11.97946644</v>
       </c>
       <c r="Q11">
-        <v>12.013394796</v>
+        <v>11.97946644</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08569384109116868</v>
+        <v>0.08602548337644025</v>
       </c>
       <c r="T11">
-        <v>0.4779179366081333</v>
+        <v>0.4818909257296066</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>40.34236141592006</v>
+        <v>36.30812527432806</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08109483503879623</v>
+        <v>0.08090356468462895</v>
       </c>
       <c r="C12">
-        <v>88.55438510336229</v>
+        <v>87.78710750831002</v>
       </c>
       <c r="D12">
-        <v>88.28438510336228</v>
+        <v>88.44110750831001</v>
       </c>
       <c r="E12">
-        <v>-49.06</v>
+        <v>-48.136</v>
       </c>
       <c r="F12">
-        <v>9.24</v>
+        <v>10.164</v>
       </c>
       <c r="G12">
         <v>9.51</v>
@@ -2265,28 +2265,28 @@
         <v>16.875</v>
       </c>
       <c r="M12">
-        <v>0.464772</v>
+        <v>0.5112492000000001</v>
       </c>
       <c r="N12">
-        <v>16.410228</v>
+        <v>16.3637508</v>
       </c>
       <c r="O12">
-        <v>4.430761560000001</v>
+        <v>4.418212716</v>
       </c>
       <c r="P12">
-        <v>11.97946644</v>
+        <v>11.945538084</v>
       </c>
       <c r="Q12">
-        <v>11.97946644</v>
+        <v>11.945538084</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08602548337644025</v>
+        <v>0.0863645782973359</v>
       </c>
       <c r="T12">
-        <v>0.4818909257296066</v>
+        <v>0.4859531955054951</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>36.30812527432806</v>
+        <v>33.0073866130255</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08090356468462895</v>
+        <v>0.08071229433046169</v>
       </c>
       <c r="C13">
-        <v>87.78710750831002</v>
+        <v>87.02038732988402</v>
       </c>
       <c r="D13">
-        <v>88.44110750831001</v>
+        <v>88.59838732988402</v>
       </c>
       <c r="E13">
-        <v>-48.136</v>
+        <v>-47.212</v>
       </c>
       <c r="F13">
-        <v>10.164</v>
+        <v>11.088</v>
       </c>
       <c r="G13">
         <v>9.51</v>
@@ -2347,28 +2347,28 @@
         <v>16.875</v>
       </c>
       <c r="M13">
-        <v>0.5112492000000001</v>
+        <v>0.5577264000000001</v>
       </c>
       <c r="N13">
-        <v>16.3637508</v>
+        <v>16.3172736</v>
       </c>
       <c r="O13">
-        <v>4.418212716</v>
+        <v>4.405663872</v>
       </c>
       <c r="P13">
-        <v>11.945538084</v>
+        <v>11.911609728</v>
       </c>
       <c r="Q13">
-        <v>11.945538084</v>
+        <v>11.911609728</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0863645782973359</v>
+        <v>0.0867113799209792</v>
       </c>
       <c r="T13">
-        <v>0.4859531955054951</v>
+        <v>0.4901077895944719</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>33.0073866130255</v>
+        <v>30.25677106194004</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08071229433046169</v>
+        <v>0.08052102397629443</v>
       </c>
       <c r="C14">
-        <v>87.02038732988402</v>
+        <v>86.25422754723883</v>
       </c>
       <c r="D14">
-        <v>88.59838732988402</v>
+        <v>88.75622754723882</v>
       </c>
       <c r="E14">
-        <v>-47.212</v>
+        <v>-46.288</v>
       </c>
       <c r="F14">
-        <v>11.088</v>
+        <v>12.012</v>
       </c>
       <c r="G14">
         <v>9.51</v>
@@ -2429,28 +2429,28 @@
         <v>16.875</v>
       </c>
       <c r="M14">
-        <v>0.5577264000000001</v>
+        <v>0.6042036</v>
       </c>
       <c r="N14">
-        <v>16.3172736</v>
+        <v>16.2707964</v>
       </c>
       <c r="O14">
-        <v>4.405663872</v>
+        <v>4.393115028</v>
       </c>
       <c r="P14">
-        <v>11.911609728</v>
+        <v>11.877681372</v>
       </c>
       <c r="Q14">
-        <v>11.911609728</v>
+        <v>11.877681372</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0867113799209792</v>
+        <v>0.08706615399574072</v>
       </c>
       <c r="T14">
-        <v>0.4901077895944719</v>
+        <v>0.4943578915935402</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>30.25677106194004</v>
+        <v>27.92932713409851</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08052102397629443</v>
+        <v>0.08032975362212716</v>
       </c>
       <c r="C15">
-        <v>86.25422754723883</v>
+        <v>85.48863116079659</v>
       </c>
       <c r="D15">
-        <v>88.75622754723882</v>
+        <v>88.91463116079659</v>
       </c>
       <c r="E15">
-        <v>-46.288</v>
+        <v>-45.364</v>
       </c>
       <c r="F15">
-        <v>12.012</v>
+        <v>12.936</v>
       </c>
       <c r="G15">
         <v>9.51</v>
@@ -2511,28 +2511,28 @@
         <v>16.875</v>
       </c>
       <c r="M15">
-        <v>0.6042036</v>
+        <v>0.6506808000000001</v>
       </c>
       <c r="N15">
-        <v>16.2707964</v>
+        <v>16.2243192</v>
       </c>
       <c r="O15">
-        <v>4.393115028</v>
+        <v>4.380566184</v>
       </c>
       <c r="P15">
-        <v>11.877681372</v>
+        <v>11.843753016</v>
       </c>
       <c r="Q15">
-        <v>11.877681372</v>
+        <v>11.843753016</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08706615399574072</v>
+        <v>0.08742917863038041</v>
       </c>
       <c r="T15">
-        <v>0.4943578915935402</v>
+        <v>0.4987068331739821</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>27.92932713409851</v>
+        <v>25.93437519594861</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08032975362212716</v>
+        <v>0.08013848326795989</v>
       </c>
       <c r="C16">
-        <v>85.48863116079659</v>
+        <v>84.7236011924372</v>
       </c>
       <c r="D16">
-        <v>88.91463116079659</v>
+        <v>89.0736011924372</v>
       </c>
       <c r="E16">
-        <v>-45.364</v>
+        <v>-44.44</v>
       </c>
       <c r="F16">
-        <v>12.936</v>
+        <v>13.86</v>
       </c>
       <c r="G16">
         <v>9.51</v>
@@ -2593,28 +2593,28 @@
         <v>16.875</v>
       </c>
       <c r="M16">
-        <v>0.6506808000000001</v>
+        <v>0.6971580000000002</v>
       </c>
       <c r="N16">
-        <v>16.2243192</v>
+        <v>16.177842</v>
       </c>
       <c r="O16">
-        <v>4.380566184</v>
+        <v>4.36801734</v>
       </c>
       <c r="P16">
-        <v>11.843753016</v>
+        <v>11.80982466</v>
       </c>
       <c r="Q16">
-        <v>11.843753016</v>
+        <v>11.80982466</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08742917863038041</v>
+        <v>0.08780074502112929</v>
       </c>
       <c r="T16">
-        <v>0.4987068331739821</v>
+        <v>0.5031581027916109</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>25.93437519594861</v>
+        <v>24.20541684955203</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08013848326795989</v>
+        <v>0.07994721291379263</v>
       </c>
       <c r="C17">
-        <v>84.7236011924372</v>
+        <v>83.95914068569046</v>
       </c>
       <c r="D17">
-        <v>89.0736011924372</v>
+        <v>89.23314068569046</v>
       </c>
       <c r="E17">
-        <v>-44.44</v>
+        <v>-43.51600000000001</v>
       </c>
       <c r="F17">
-        <v>13.86</v>
+        <v>14.784</v>
       </c>
       <c r="G17">
         <v>9.51</v>
@@ -2675,28 +2675,28 @@
         <v>16.875</v>
       </c>
       <c r="M17">
-        <v>0.6971580000000001</v>
+        <v>0.7436352000000001</v>
       </c>
       <c r="N17">
-        <v>16.177842</v>
+        <v>16.1313648</v>
       </c>
       <c r="O17">
-        <v>4.36801734</v>
+        <v>4.355468496</v>
       </c>
       <c r="P17">
-        <v>11.80982466</v>
+        <v>11.775896304</v>
       </c>
       <c r="Q17">
-        <v>11.80982466</v>
+        <v>11.775896304</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08780074502112929</v>
+        <v>0.08818115823070552</v>
       </c>
       <c r="T17">
-        <v>0.5031581027916109</v>
+        <v>0.5077153550191833</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>24.20541684955203</v>
+        <v>22.69257829645504</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07994721291379263</v>
+        <v>0.07975594255962536</v>
       </c>
       <c r="C18">
-        <v>83.95914068569046</v>
+        <v>83.19525270593037</v>
       </c>
       <c r="D18">
-        <v>89.23314068569046</v>
+        <v>89.39325270593037</v>
       </c>
       <c r="E18">
-        <v>-43.51600000000001</v>
+        <v>-42.592</v>
       </c>
       <c r="F18">
-        <v>14.784</v>
+        <v>15.708</v>
       </c>
       <c r="G18">
         <v>9.51</v>
@@ -2757,28 +2757,28 @@
         <v>16.875</v>
       </c>
       <c r="M18">
-        <v>0.7436352000000001</v>
+        <v>0.7901124</v>
       </c>
       <c r="N18">
-        <v>16.1313648</v>
+        <v>16.0848876</v>
       </c>
       <c r="O18">
-        <v>4.355468496</v>
+        <v>4.342919652</v>
       </c>
       <c r="P18">
-        <v>11.775896304</v>
+        <v>11.741967948</v>
       </c>
       <c r="Q18">
-        <v>11.775896304</v>
+        <v>11.741967948</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08818115823070552</v>
+        <v>0.08857073802364501</v>
       </c>
       <c r="T18">
-        <v>0.5077153550191833</v>
+        <v>0.5123824205534441</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>22.69257829645504</v>
+        <v>21.35772074960474</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07975594255962536</v>
+        <v>0.0795646722054581</v>
       </c>
       <c r="C19">
-        <v>83.19525270593037</v>
+        <v>82.43194034057137</v>
       </c>
       <c r="D19">
-        <v>89.39325270593037</v>
+        <v>89.55394034057137</v>
       </c>
       <c r="E19">
-        <v>-42.592</v>
+        <v>-41.66800000000001</v>
       </c>
       <c r="F19">
-        <v>15.708</v>
+        <v>16.632</v>
       </c>
       <c r="G19">
         <v>9.51</v>
@@ -2839,28 +2839,28 @@
         <v>16.875</v>
       </c>
       <c r="M19">
-        <v>0.7901124</v>
+        <v>0.8365896</v>
       </c>
       <c r="N19">
-        <v>16.0848876</v>
+        <v>16.0384104</v>
       </c>
       <c r="O19">
-        <v>4.342919652</v>
+        <v>4.330370808000001</v>
       </c>
       <c r="P19">
-        <v>11.741967948</v>
+        <v>11.708039592</v>
       </c>
       <c r="Q19">
-        <v>11.741967948</v>
+        <v>11.708039592</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08857073802364501</v>
+        <v>0.08896981976275378</v>
       </c>
       <c r="T19">
-        <v>0.5123824205534441</v>
+        <v>0.5171633169543942</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>21.35772074960474</v>
+        <v>20.17118070796003</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07956467220545811</v>
+        <v>0.07937340185129083</v>
       </c>
       <c r="C20">
-        <v>82.43194034057136</v>
+        <v>81.66920669926694</v>
       </c>
       <c r="D20">
-        <v>89.55394034057136</v>
+        <v>89.71520669926693</v>
       </c>
       <c r="E20">
-        <v>-41.66800000000001</v>
+        <v>-40.744</v>
       </c>
       <c r="F20">
-        <v>16.632</v>
+        <v>17.556</v>
       </c>
       <c r="G20">
         <v>9.51</v>
@@ -2921,28 +2921,28 @@
         <v>16.875</v>
       </c>
       <c r="M20">
-        <v>0.8365896</v>
+        <v>0.8830668</v>
       </c>
       <c r="N20">
-        <v>16.0384104</v>
+        <v>15.9919332</v>
       </c>
       <c r="O20">
-        <v>4.330370808000001</v>
+        <v>4.317821964</v>
       </c>
       <c r="P20">
-        <v>11.708039592</v>
+        <v>11.674111236</v>
       </c>
       <c r="Q20">
-        <v>11.708039592</v>
+        <v>11.674111236</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08896981976275378</v>
+        <v>0.08937875537196399</v>
       </c>
       <c r="T20">
-        <v>0.5171633169543942</v>
+        <v>0.5220622601800592</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>20.17118070796003</v>
+        <v>19.1095396180674</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07937340185129083</v>
+        <v>0.07918213149712358</v>
       </c>
       <c r="C21">
-        <v>81.66920669926694</v>
+        <v>80.90705491410991</v>
       </c>
       <c r="D21">
-        <v>89.71520669926693</v>
+        <v>89.87705491410991</v>
       </c>
       <c r="E21">
-        <v>-40.744</v>
+        <v>-39.82000000000001</v>
       </c>
       <c r="F21">
-        <v>17.556</v>
+        <v>18.48</v>
       </c>
       <c r="G21">
         <v>9.51</v>
@@ -3003,28 +3003,28 @@
         <v>16.875</v>
       </c>
       <c r="M21">
-        <v>0.8830668</v>
+        <v>0.9295439999999999</v>
       </c>
       <c r="N21">
-        <v>15.9919332</v>
+        <v>15.945456</v>
       </c>
       <c r="O21">
-        <v>4.317821964</v>
+        <v>4.305273120000001</v>
       </c>
       <c r="P21">
-        <v>11.674111236</v>
+        <v>11.64018288</v>
       </c>
       <c r="Q21">
-        <v>11.674111236</v>
+        <v>11.64018288</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08937875537196399</v>
+        <v>0.08979791437140447</v>
       </c>
       <c r="T21">
-        <v>0.5220622601800592</v>
+        <v>0.5270836769863657</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>19.1095396180674</v>
+        <v>18.15406263716403</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07918213149712358</v>
+        <v>0.07899086114295631</v>
       </c>
       <c r="C22">
-        <v>80.90705491410991</v>
+        <v>80.14548813983561</v>
       </c>
       <c r="D22">
-        <v>89.87705491410991</v>
+        <v>90.0394881398356</v>
       </c>
       <c r="E22">
-        <v>-39.82000000000001</v>
+        <v>-38.896</v>
       </c>
       <c r="F22">
-        <v>18.48</v>
+        <v>19.404</v>
       </c>
       <c r="G22">
         <v>9.51</v>
@@ -3085,28 +3085,28 @@
         <v>16.875</v>
       </c>
       <c r="M22">
-        <v>0.9295439999999999</v>
+        <v>0.9760212000000001</v>
       </c>
       <c r="N22">
-        <v>15.945456</v>
+        <v>15.8989788</v>
       </c>
       <c r="O22">
-        <v>4.305273120000001</v>
+        <v>4.292724276</v>
       </c>
       <c r="P22">
-        <v>11.64018288</v>
+        <v>11.606254524</v>
       </c>
       <c r="Q22">
-        <v>11.64018288</v>
+        <v>11.606254524</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08979791437140447</v>
+        <v>0.09022768499108393</v>
       </c>
       <c r="T22">
-        <v>0.5270836769863657</v>
+        <v>0.5322322182687813</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>18.15406263716403</v>
+        <v>17.28958346396574</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07899086114295631</v>
+        <v>0.07879959078878904</v>
       </c>
       <c r="C23">
-        <v>80.14548813983561</v>
+        <v>79.38450955402652</v>
       </c>
       <c r="D23">
-        <v>90.0394881398356</v>
+        <v>90.20250955402652</v>
       </c>
       <c r="E23">
-        <v>-38.896</v>
+        <v>-37.972</v>
       </c>
       <c r="F23">
-        <v>19.404</v>
+        <v>20.328</v>
       </c>
       <c r="G23">
         <v>9.51</v>
@@ -3167,28 +3167,28 @@
         <v>16.875</v>
       </c>
       <c r="M23">
-        <v>0.9760211999999999</v>
+        <v>1.0224984</v>
       </c>
       <c r="N23">
-        <v>15.8989788</v>
+        <v>15.8525016</v>
       </c>
       <c r="O23">
-        <v>4.292724276</v>
+        <v>4.280175432</v>
       </c>
       <c r="P23">
-        <v>11.606254524</v>
+        <v>11.572326168</v>
       </c>
       <c r="Q23">
-        <v>11.606254524</v>
+        <v>11.572326168</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09022768499108393</v>
+        <v>0.09066847537024235</v>
       </c>
       <c r="T23">
-        <v>0.5322322182687813</v>
+        <v>0.5375127734302332</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>17.28958346396574</v>
+        <v>16.50369330651275</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07879959078878904</v>
+        <v>0.07860832043462176</v>
       </c>
       <c r="C24">
-        <v>79.38450955402652</v>
+        <v>78.62412235731969</v>
       </c>
       <c r="D24">
-        <v>90.20250955402652</v>
+        <v>90.36612235731968</v>
       </c>
       <c r="E24">
-        <v>-37.972</v>
+        <v>-37.048</v>
       </c>
       <c r="F24">
-        <v>20.328</v>
+        <v>21.252</v>
       </c>
       <c r="G24">
         <v>9.51</v>
@@ -3249,28 +3249,28 @@
         <v>16.875</v>
       </c>
       <c r="M24">
-        <v>1.0224984</v>
+        <v>1.0689756</v>
       </c>
       <c r="N24">
-        <v>15.8525016</v>
+        <v>15.8060244</v>
       </c>
       <c r="O24">
-        <v>4.280175432</v>
+        <v>4.267626588000001</v>
       </c>
       <c r="P24">
-        <v>11.572326168</v>
+        <v>11.538397812</v>
       </c>
       <c r="Q24">
-        <v>11.572326168</v>
+        <v>11.538397812</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09066847537024235</v>
+        <v>0.09112071485015814</v>
       </c>
       <c r="T24">
-        <v>0.5375127734302332</v>
+        <v>0.5429304858686059</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>16.50369330651275</v>
+        <v>15.78614142362089</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07860832043462176</v>
+        <v>0.07841705008045451</v>
       </c>
       <c r="C25">
-        <v>78.62412235731969</v>
+        <v>77.86432977361605</v>
       </c>
       <c r="D25">
-        <v>90.36612235731968</v>
+        <v>90.53032977361605</v>
       </c>
       <c r="E25">
-        <v>-37.048</v>
+        <v>-36.124</v>
       </c>
       <c r="F25">
-        <v>21.252</v>
+        <v>22.176</v>
       </c>
       <c r="G25">
         <v>9.51</v>
@@ -3331,28 +3331,28 @@
         <v>16.875</v>
       </c>
       <c r="M25">
-        <v>1.0689756</v>
+        <v>1.1154528</v>
       </c>
       <c r="N25">
-        <v>15.8060244</v>
+        <v>15.7595472</v>
       </c>
       <c r="O25">
-        <v>4.267626588000001</v>
+        <v>4.255077744</v>
       </c>
       <c r="P25">
-        <v>11.538397812</v>
+        <v>11.504469456</v>
       </c>
       <c r="Q25">
-        <v>11.538397812</v>
+        <v>11.504469456</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09112071485015814</v>
+        <v>0.09158485536901909</v>
       </c>
       <c r="T25">
-        <v>0.5429304858686059</v>
+        <v>0.5484907696869358</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>15.78614142362089</v>
+        <v>15.12838553097002</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07841705008045451</v>
+        <v>0.07822577972628723</v>
       </c>
       <c r="C26">
-        <v>77.86432977361605</v>
+        <v>77.10513505029235</v>
       </c>
       <c r="D26">
-        <v>90.53032977361605</v>
+        <v>90.69513505029234</v>
       </c>
       <c r="E26">
-        <v>-36.124</v>
+        <v>-35.2</v>
       </c>
       <c r="F26">
-        <v>22.176</v>
+        <v>23.1</v>
       </c>
       <c r="G26">
         <v>9.51</v>
@@ -3413,28 +3413,28 @@
         <v>16.875</v>
       </c>
       <c r="M26">
-        <v>1.1154528</v>
+        <v>1.16193</v>
       </c>
       <c r="N26">
-        <v>15.7595472</v>
+        <v>15.71307</v>
       </c>
       <c r="O26">
-        <v>4.255077744</v>
+        <v>4.2425289</v>
       </c>
       <c r="P26">
-        <v>11.504469456</v>
+        <v>11.4705411</v>
       </c>
       <c r="Q26">
-        <v>11.504469456</v>
+        <v>11.4705411</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09158485536901909</v>
+        <v>0.09206137296838299</v>
       </c>
       <c r="T26">
-        <v>0.5484907696869358</v>
+        <v>0.5541993277404212</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>15.12838553097002</v>
+        <v>14.52325010973122</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07822577972628723</v>
+        <v>0.07803450937211998</v>
       </c>
       <c r="C27">
-        <v>77.10513505029235</v>
+        <v>76.34654145841493</v>
       </c>
       <c r="D27">
-        <v>90.69513505029234</v>
+        <v>90.86054145841493</v>
       </c>
       <c r="E27">
-        <v>-35.2</v>
+        <v>-34.276</v>
       </c>
       <c r="F27">
-        <v>23.1</v>
+        <v>24.024</v>
       </c>
       <c r="G27">
         <v>9.51</v>
@@ -3495,28 +3495,28 @@
         <v>16.875</v>
       </c>
       <c r="M27">
-        <v>1.16193</v>
+        <v>1.2084072</v>
       </c>
       <c r="N27">
-        <v>15.71307</v>
+        <v>15.6665928</v>
       </c>
       <c r="O27">
-        <v>4.2425289</v>
+        <v>4.229980056</v>
       </c>
       <c r="P27">
-        <v>11.4705411</v>
+        <v>11.436612744</v>
       </c>
       <c r="Q27">
-        <v>11.4705411</v>
+        <v>11.436612744</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09206137296838299</v>
+        <v>0.09255076942178375</v>
       </c>
       <c r="T27">
-        <v>0.5541993277404212</v>
+        <v>0.5600621711467034</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>14.52325010973122</v>
+        <v>13.96466356704925</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07803450937211998</v>
+        <v>0.0778432390179527</v>
       </c>
       <c r="C28">
-        <v>76.34654145841493</v>
+        <v>75.58855229295654</v>
       </c>
       <c r="D28">
-        <v>90.86054145841493</v>
+        <v>91.02655229295654</v>
       </c>
       <c r="E28">
-        <v>-34.276</v>
+        <v>-33.352</v>
       </c>
       <c r="F28">
-        <v>24.024</v>
+        <v>24.948</v>
       </c>
       <c r="G28">
         <v>9.51</v>
@@ -3577,28 +3577,28 @@
         <v>16.875</v>
       </c>
       <c r="M28">
-        <v>1.2084072</v>
+        <v>1.2548844</v>
       </c>
       <c r="N28">
-        <v>15.6665928</v>
+        <v>15.6201156</v>
       </c>
       <c r="O28">
-        <v>4.229980056</v>
+        <v>4.217431212</v>
       </c>
       <c r="P28">
-        <v>11.436612744</v>
+        <v>11.402684388</v>
       </c>
       <c r="Q28">
-        <v>11.436612744</v>
+        <v>11.402684388</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09255076942178375</v>
+        <v>0.09305357399719549</v>
       </c>
       <c r="T28">
-        <v>0.5600621711467034</v>
+        <v>0.5660856403997332</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>13.96466356704925</v>
+        <v>13.44745380530669</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0778432390179527</v>
+        <v>0.07765196866378543</v>
       </c>
       <c r="C29">
-        <v>75.58855229295654</v>
+        <v>74.83117087301481</v>
       </c>
       <c r="D29">
-        <v>91.02655229295654</v>
+        <v>91.19317087301481</v>
       </c>
       <c r="E29">
-        <v>-33.352</v>
+        <v>-32.428</v>
       </c>
       <c r="F29">
-        <v>24.948</v>
+        <v>25.872</v>
       </c>
       <c r="G29">
         <v>9.51</v>
@@ -3659,28 +3659,28 @@
         <v>16.875</v>
       </c>
       <c r="M29">
-        <v>1.2548844</v>
+        <v>1.3013616</v>
       </c>
       <c r="N29">
-        <v>15.6201156</v>
+        <v>15.5736384</v>
       </c>
       <c r="O29">
-        <v>4.217431212</v>
+        <v>4.204882368000001</v>
       </c>
       <c r="P29">
-        <v>11.402684388</v>
+        <v>11.368756032</v>
       </c>
       <c r="Q29">
-        <v>11.402684388</v>
+        <v>11.368756032</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09305357399719549</v>
+        <v>0.09357034536636867</v>
       </c>
       <c r="T29">
-        <v>0.5660856403997332</v>
+        <v>0.5722764282431249</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>13.44745380530669</v>
+        <v>12.96718759797431</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07765196866378543</v>
+        <v>0.07777824830961817</v>
       </c>
       <c r="C30">
-        <v>74.83117087301481</v>
+        <v>73.79709837463609</v>
       </c>
       <c r="D30">
-        <v>91.19317087301481</v>
+        <v>91.08309837463609</v>
       </c>
       <c r="E30">
-        <v>-32.428</v>
+        <v>-31.504</v>
       </c>
       <c r="F30">
-        <v>25.872</v>
+        <v>26.79600000000001</v>
       </c>
       <c r="G30">
         <v>9.51</v>
@@ -3741,45 +3741,45 @@
         <v>16.875</v>
       </c>
       <c r="M30">
-        <v>1.3013616</v>
+        <v>1.3880328</v>
       </c>
       <c r="N30">
-        <v>15.5736384</v>
+        <v>15.4869672</v>
       </c>
       <c r="O30">
-        <v>4.204882368000001</v>
+        <v>4.181481144</v>
       </c>
       <c r="P30">
-        <v>11.368756032</v>
+        <v>11.305486056</v>
       </c>
       <c r="Q30">
-        <v>11.368756032</v>
+        <v>11.305486056</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09357034536636867</v>
+        <v>0.09410167367551855</v>
       </c>
       <c r="T30">
-        <v>0.5722764282431249</v>
+        <v>0.5786416044764712</v>
       </c>
       <c r="U30">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V30">
         <v>0.27</v>
       </c>
       <c r="W30">
-        <v>0.03671899999999999</v>
+        <v>0.037814</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y30">
-        <v>12.96718759797431</v>
+        <v>12.15749368458728</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07777824830961817</v>
+        <v>0.0775979279554509</v>
       </c>
       <c r="C31">
-        <v>73.79709837463611</v>
+        <v>73.03035714674013</v>
       </c>
       <c r="D31">
-        <v>91.08309837463609</v>
+        <v>91.24035714674012</v>
       </c>
       <c r="E31">
-        <v>-31.504</v>
+        <v>-30.58</v>
       </c>
       <c r="F31">
-        <v>26.796</v>
+        <v>27.72</v>
       </c>
       <c r="G31">
         <v>9.51</v>
@@ -3823,28 +3823,28 @@
         <v>16.875</v>
       </c>
       <c r="M31">
-        <v>1.3880328</v>
+        <v>1.435896</v>
       </c>
       <c r="N31">
-        <v>15.4869672</v>
+        <v>15.439104</v>
       </c>
       <c r="O31">
-        <v>4.181481144</v>
+        <v>4.16855808</v>
       </c>
       <c r="P31">
-        <v>11.305486056</v>
+        <v>11.27054592</v>
       </c>
       <c r="Q31">
-        <v>11.305486056</v>
+        <v>11.27054592</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09410167367551855</v>
+        <v>0.09464818279350129</v>
       </c>
       <c r="T31">
-        <v>0.5786416044764712</v>
+        <v>0.5851886428879132</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>12.15749368458728</v>
+        <v>11.75224389510104</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0775979279554509</v>
+        <v>0.07741760760128365</v>
       </c>
       <c r="C32">
-        <v>73.03035714674013</v>
+        <v>72.26415988569693</v>
       </c>
       <c r="D32">
-        <v>91.24035714674012</v>
+        <v>91.39815988569693</v>
       </c>
       <c r="E32">
-        <v>-30.58</v>
+        <v>-29.656</v>
       </c>
       <c r="F32">
-        <v>27.72</v>
+        <v>28.644</v>
       </c>
       <c r="G32">
         <v>9.51</v>
@@ -3905,28 +3905,28 @@
         <v>16.875</v>
       </c>
       <c r="M32">
-        <v>1.435896</v>
+        <v>1.4837592</v>
       </c>
       <c r="N32">
-        <v>15.439104</v>
+        <v>15.3912408</v>
       </c>
       <c r="O32">
-        <v>4.16855808</v>
+        <v>4.155635016000001</v>
       </c>
       <c r="P32">
-        <v>11.27054592</v>
+        <v>11.235605784</v>
       </c>
       <c r="Q32">
-        <v>11.27054592</v>
+        <v>11.235605784</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09464818279350129</v>
+        <v>0.09521053275548355</v>
       </c>
       <c r="T32">
-        <v>0.5851886428879132</v>
+        <v>0.5919254505286723</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>11.75224389510104</v>
+        <v>11.37313925332358</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07741760760128365</v>
+        <v>0.07723728724711636</v>
       </c>
       <c r="C33">
-        <v>72.26415988569693</v>
+        <v>71.49850941881397</v>
       </c>
       <c r="D33">
-        <v>91.39815988569693</v>
+        <v>91.55650941881396</v>
       </c>
       <c r="E33">
-        <v>-29.656</v>
+        <v>-28.732</v>
       </c>
       <c r="F33">
-        <v>28.644</v>
+        <v>29.568</v>
       </c>
       <c r="G33">
         <v>9.51</v>
@@ -3987,28 +3987,28 @@
         <v>16.875</v>
       </c>
       <c r="M33">
-        <v>1.4837592</v>
+        <v>1.5316224</v>
       </c>
       <c r="N33">
-        <v>15.3912408</v>
+        <v>15.3433776</v>
       </c>
       <c r="O33">
-        <v>4.155635016000001</v>
+        <v>4.142711952</v>
       </c>
       <c r="P33">
-        <v>11.235605784</v>
+        <v>11.200665648</v>
       </c>
       <c r="Q33">
-        <v>11.235605784</v>
+        <v>11.200665648</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09521053275548355</v>
+        <v>0.09578942242222996</v>
       </c>
       <c r="T33">
-        <v>0.5919254505286723</v>
+        <v>0.5988603995706302</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>11.37313925332358</v>
+        <v>11.01772865165722</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07723728724711636</v>
+        <v>0.07705696689294911</v>
       </c>
       <c r="C34">
-        <v>71.49850941881397</v>
+        <v>70.73340859302601</v>
       </c>
       <c r="D34">
-        <v>91.55650941881396</v>
+        <v>91.71540859302601</v>
       </c>
       <c r="E34">
-        <v>-28.732</v>
+        <v>-27.808</v>
       </c>
       <c r="F34">
-        <v>29.568</v>
+        <v>30.492</v>
       </c>
       <c r="G34">
         <v>9.51</v>
@@ -4069,28 +4069,28 @@
         <v>16.875</v>
       </c>
       <c r="M34">
-        <v>1.5316224</v>
+        <v>1.5794856</v>
       </c>
       <c r="N34">
-        <v>15.3433776</v>
+        <v>15.2955144</v>
       </c>
       <c r="O34">
-        <v>4.142711952</v>
+        <v>4.129788888</v>
       </c>
       <c r="P34">
-        <v>11.200665648</v>
+        <v>11.165725512</v>
       </c>
       <c r="Q34">
-        <v>11.200665648</v>
+        <v>11.165725512</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09578942242222996</v>
+        <v>0.09638559237753599</v>
       </c>
       <c r="T34">
-        <v>0.5988603995706302</v>
+        <v>0.6060023620168257</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>11.01772865165722</v>
+        <v>10.68385808645549</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07705696689294911</v>
+        <v>0.07687664653878185</v>
       </c>
       <c r="C35">
-        <v>70.73340859302601</v>
+        <v>69.96886027506619</v>
       </c>
       <c r="D35">
-        <v>91.71540859302601</v>
+        <v>91.8748602750662</v>
       </c>
       <c r="E35">
-        <v>-27.808</v>
+        <v>-26.884</v>
       </c>
       <c r="F35">
-        <v>30.492</v>
+        <v>31.416</v>
       </c>
       <c r="G35">
         <v>9.51</v>
@@ -4151,28 +4151,28 @@
         <v>16.875</v>
       </c>
       <c r="M35">
-        <v>1.5794856</v>
+        <v>1.6273488</v>
       </c>
       <c r="N35">
-        <v>15.2955144</v>
+        <v>15.2476512</v>
       </c>
       <c r="O35">
-        <v>4.129788888</v>
+        <v>4.116865824</v>
       </c>
       <c r="P35">
-        <v>11.165725512</v>
+        <v>11.130785376</v>
       </c>
       <c r="Q35">
-        <v>11.165725512</v>
+        <v>11.130785376</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09638559237753599</v>
+        <v>0.09699982808906341</v>
       </c>
       <c r="T35">
-        <v>0.6060023620168257</v>
+        <v>0.6133607475674513</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>10.68385808645549</v>
+        <v>10.36962696626562</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07687664653878185</v>
+        <v>0.07669632618461455</v>
       </c>
       <c r="C36">
-        <v>69.96886027506619</v>
+        <v>69.20486735163809</v>
       </c>
       <c r="D36">
-        <v>91.8748602750662</v>
+        <v>92.03486735163808</v>
       </c>
       <c r="E36">
-        <v>-26.884</v>
+        <v>-25.96</v>
       </c>
       <c r="F36">
-        <v>31.416</v>
+        <v>32.34</v>
       </c>
       <c r="G36">
         <v>9.51</v>
@@ -4233,28 +4233,28 @@
         <v>16.875</v>
       </c>
       <c r="M36">
-        <v>1.6273488</v>
+        <v>1.675212</v>
       </c>
       <c r="N36">
-        <v>15.2476512</v>
+        <v>15.199788</v>
       </c>
       <c r="O36">
-        <v>4.116865824</v>
+        <v>4.10394276</v>
       </c>
       <c r="P36">
-        <v>11.130785376</v>
+        <v>11.09584524</v>
       </c>
       <c r="Q36">
-        <v>11.130785376</v>
+        <v>11.09584524</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09699982808906341</v>
+        <v>0.0976329633609455</v>
       </c>
       <c r="T36">
-        <v>0.6133607475674513</v>
+        <v>0.620945544981173</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>10.36962696626562</v>
+        <v>10.0733519100866</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07669632618461455</v>
+        <v>0.0769627658304473</v>
       </c>
       <c r="C37">
-        <v>69.20486735163809</v>
+        <v>68.04463855634262</v>
       </c>
       <c r="D37">
-        <v>92.03486735163808</v>
+        <v>91.79863855634261</v>
       </c>
       <c r="E37">
-        <v>-25.96</v>
+        <v>-25.036</v>
       </c>
       <c r="F37">
-        <v>32.34</v>
+        <v>33.264</v>
       </c>
       <c r="G37">
         <v>9.51</v>
@@ -4315,45 +4315,45 @@
         <v>16.875</v>
       </c>
       <c r="M37">
-        <v>1.675212</v>
+        <v>1.779624</v>
       </c>
       <c r="N37">
-        <v>15.199788</v>
+        <v>15.095376</v>
       </c>
       <c r="O37">
-        <v>4.10394276</v>
+        <v>4.07575152</v>
       </c>
       <c r="P37">
-        <v>11.09584524</v>
+        <v>11.01962448</v>
       </c>
       <c r="Q37">
-        <v>11.09584524</v>
+        <v>11.01962448</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.0976329633609455</v>
+        <v>0.09828588411007393</v>
       </c>
       <c r="T37">
-        <v>0.620945544981173</v>
+        <v>0.6287673673140737</v>
       </c>
       <c r="U37">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V37">
         <v>0.27</v>
       </c>
       <c r="W37">
-        <v>0.037814</v>
+        <v>0.039055</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>10.0733519100866</v>
+        <v>9.482340089816725</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07696276583044731</v>
+        <v>0.07679485547628005</v>
       </c>
       <c r="C38">
-        <v>68.04463855634262</v>
+        <v>67.26936848813858</v>
       </c>
       <c r="D38">
-        <v>91.79863855634261</v>
+        <v>91.94736848813858</v>
       </c>
       <c r="E38">
-        <v>-25.036</v>
+        <v>-24.112</v>
       </c>
       <c r="F38">
-        <v>33.264</v>
+        <v>34.188</v>
       </c>
       <c r="G38">
         <v>9.51</v>
@@ -4397,28 +4397,28 @@
         <v>16.875</v>
       </c>
       <c r="M38">
-        <v>1.779624</v>
+        <v>1.829058</v>
       </c>
       <c r="N38">
-        <v>15.095376</v>
+        <v>15.045942</v>
       </c>
       <c r="O38">
-        <v>4.07575152</v>
+        <v>4.062404340000001</v>
       </c>
       <c r="P38">
-        <v>11.01962448</v>
+        <v>10.98353766</v>
       </c>
       <c r="Q38">
-        <v>11.01962448</v>
+        <v>10.98353766</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09828588411007393</v>
+        <v>0.09895953250203182</v>
       </c>
       <c r="T38">
-        <v>0.6287673673140737</v>
+        <v>0.6368375014670663</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>9.482340089816725</v>
+        <v>9.226060627929787</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07679485547628005</v>
+        <v>0.07662694512211278</v>
       </c>
       <c r="C39">
-        <v>67.26936848813858</v>
+        <v>66.49458113929447</v>
       </c>
       <c r="D39">
-        <v>91.94736848813858</v>
+        <v>92.09658113929446</v>
       </c>
       <c r="E39">
-        <v>-24.112</v>
+        <v>-23.188</v>
       </c>
       <c r="F39">
-        <v>34.188</v>
+        <v>35.112</v>
       </c>
       <c r="G39">
         <v>9.51</v>
@@ -4479,28 +4479,28 @@
         <v>16.875</v>
       </c>
       <c r="M39">
-        <v>1.829058</v>
+        <v>1.878492</v>
       </c>
       <c r="N39">
-        <v>15.045942</v>
+        <v>14.996508</v>
       </c>
       <c r="O39">
-        <v>4.062404340000001</v>
+        <v>4.04905716</v>
       </c>
       <c r="P39">
-        <v>10.98353766</v>
+        <v>10.94745084</v>
       </c>
       <c r="Q39">
-        <v>10.98353766</v>
+        <v>10.94745084</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09895953250203182</v>
+        <v>0.09965491148727867</v>
       </c>
       <c r="T39">
-        <v>0.6368375014670663</v>
+        <v>0.6451679625282201</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>9.226060627929787</v>
+        <v>8.98326955877374</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07662694512211278</v>
+        <v>0.07645903476794552</v>
       </c>
       <c r="C40">
-        <v>66.49458113929447</v>
+        <v>65.72027886370834</v>
       </c>
       <c r="D40">
-        <v>92.09658113929446</v>
+        <v>92.24627886370834</v>
       </c>
       <c r="E40">
-        <v>-23.188</v>
+        <v>-22.264</v>
       </c>
       <c r="F40">
-        <v>35.112</v>
+        <v>36.036</v>
       </c>
       <c r="G40">
         <v>9.51</v>
@@ -4561,28 +4561,28 @@
         <v>16.875</v>
       </c>
       <c r="M40">
-        <v>1.878492</v>
+        <v>1.927926</v>
       </c>
       <c r="N40">
-        <v>14.996508</v>
+        <v>14.947074</v>
       </c>
       <c r="O40">
-        <v>4.04905716</v>
+        <v>4.03570998</v>
       </c>
       <c r="P40">
-        <v>10.94745084</v>
+        <v>10.91136402</v>
       </c>
       <c r="Q40">
-        <v>10.94745084</v>
+        <v>10.91136402</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09965491148727867</v>
+        <v>0.1003730897835172</v>
       </c>
       <c r="T40">
-        <v>0.6451679625282201</v>
+        <v>0.6537715534602314</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.98326955877374</v>
+        <v>8.752929313676978</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07645903476794552</v>
+        <v>0.07629112441377825</v>
       </c>
       <c r="C41">
-        <v>65.72027886370834</v>
+        <v>64.94646403060776</v>
       </c>
       <c r="D41">
-        <v>92.24627886370834</v>
+        <v>92.39646403060775</v>
       </c>
       <c r="E41">
-        <v>-22.264</v>
+        <v>-21.34</v>
       </c>
       <c r="F41">
-        <v>36.036</v>
+        <v>36.96</v>
       </c>
       <c r="G41">
         <v>9.51</v>
@@ -4643,28 +4643,28 @@
         <v>16.875</v>
       </c>
       <c r="M41">
-        <v>1.927926</v>
+        <v>1.97736</v>
       </c>
       <c r="N41">
-        <v>14.947074</v>
+        <v>14.89764</v>
       </c>
       <c r="O41">
-        <v>4.03570998</v>
+        <v>4.0223628</v>
       </c>
       <c r="P41">
-        <v>10.91136402</v>
+        <v>10.8752772</v>
       </c>
       <c r="Q41">
-        <v>10.91136402</v>
+        <v>10.8752772</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1003730897835172</v>
+        <v>0.1011152073562971</v>
       </c>
       <c r="T41">
-        <v>0.6537715534602314</v>
+        <v>0.662661930756643</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>8.752929313676978</v>
+        <v>8.534106080835052</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07629112441377825</v>
+        <v>0.07612321405961098</v>
       </c>
       <c r="C42">
-        <v>64.94646403060776</v>
+        <v>64.17313902467464</v>
       </c>
       <c r="D42">
-        <v>92.39646403060775</v>
+        <v>92.54713902467465</v>
       </c>
       <c r="E42">
-        <v>-21.34</v>
+        <v>-20.416</v>
       </c>
       <c r="F42">
-        <v>36.96</v>
+        <v>37.88400000000001</v>
       </c>
       <c r="G42">
         <v>9.51</v>
@@ -4725,28 +4725,28 @@
         <v>16.875</v>
       </c>
       <c r="M42">
-        <v>1.97736</v>
+        <v>2.026794</v>
       </c>
       <c r="N42">
-        <v>14.89764</v>
+        <v>14.848206</v>
       </c>
       <c r="O42">
-        <v>4.0223628</v>
+        <v>4.00901562</v>
       </c>
       <c r="P42">
-        <v>10.8752772</v>
+        <v>10.83919038</v>
       </c>
       <c r="Q42">
-        <v>10.8752772</v>
+        <v>10.83919038</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1011152073562971</v>
+        <v>0.1018824814569678</v>
       </c>
       <c r="T42">
-        <v>0.662661930756643</v>
+        <v>0.6718536767749669</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>8.534106080835052</v>
+        <v>8.325957152034196</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07612321405961098</v>
+        <v>0.07595530370544371</v>
       </c>
       <c r="C43">
-        <v>64.17313902467464</v>
+        <v>63.40030624617165</v>
       </c>
       <c r="D43">
-        <v>92.54713902467465</v>
+        <v>92.69830624617165</v>
       </c>
       <c r="E43">
-        <v>-20.416</v>
+        <v>-19.492</v>
       </c>
       <c r="F43">
-        <v>37.88400000000001</v>
+        <v>38.80800000000001</v>
       </c>
       <c r="G43">
         <v>9.51</v>
@@ -4807,28 +4807,28 @@
         <v>16.875</v>
       </c>
       <c r="M43">
-        <v>2.026794</v>
+        <v>2.076228</v>
       </c>
       <c r="N43">
-        <v>14.848206</v>
+        <v>14.798772</v>
       </c>
       <c r="O43">
-        <v>4.00901562</v>
+        <v>3.99566844</v>
       </c>
       <c r="P43">
-        <v>10.83919038</v>
+        <v>10.80310356</v>
       </c>
       <c r="Q43">
-        <v>10.83919038</v>
+        <v>10.80310356</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1018824814569678</v>
+        <v>0.1026762132852478</v>
       </c>
       <c r="T43">
-        <v>0.6718536767749669</v>
+        <v>0.6813623795525434</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>8.325957152034196</v>
+        <v>8.127720076985764</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07595530370544372</v>
+        <v>0.07578739335127646</v>
       </c>
       <c r="C44">
-        <v>63.40030624617165</v>
+        <v>62.62796811106942</v>
       </c>
       <c r="D44">
-        <v>92.69830624617164</v>
+        <v>92.84996811106942</v>
       </c>
       <c r="E44">
-        <v>-19.492</v>
+        <v>-18.568</v>
       </c>
       <c r="F44">
-        <v>38.808</v>
+        <v>39.732</v>
       </c>
       <c r="G44">
         <v>9.51</v>
@@ -4889,28 +4889,28 @@
         <v>16.875</v>
       </c>
       <c r="M44">
-        <v>2.076228</v>
+        <v>2.125662</v>
       </c>
       <c r="N44">
-        <v>14.798772</v>
+        <v>14.749338</v>
       </c>
       <c r="O44">
-        <v>3.99566844</v>
+        <v>3.98232126</v>
       </c>
       <c r="P44">
-        <v>10.80310356</v>
+        <v>10.76701674</v>
       </c>
       <c r="Q44">
-        <v>10.80310356</v>
+        <v>10.76701674</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1026762132852478</v>
+        <v>0.1034977953531166</v>
       </c>
       <c r="T44">
-        <v>0.6813623795525432</v>
+        <v>0.6912047210240698</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>8.127720076985764</v>
+        <v>7.938703331009353</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07578739335127646</v>
+        <v>0.07561948299710919</v>
       </c>
       <c r="C45">
-        <v>62.62796811106942</v>
+        <v>61.85612705117542</v>
       </c>
       <c r="D45">
-        <v>92.84996811106942</v>
+        <v>93.00212705117542</v>
       </c>
       <c r="E45">
-        <v>-18.568</v>
+        <v>-17.644</v>
       </c>
       <c r="F45">
-        <v>39.732</v>
+        <v>40.65600000000001</v>
       </c>
       <c r="G45">
         <v>9.51</v>
@@ -4971,28 +4971,28 @@
         <v>16.875</v>
       </c>
       <c r="M45">
-        <v>2.125662</v>
+        <v>2.175096</v>
       </c>
       <c r="N45">
-        <v>14.749338</v>
+        <v>14.699904</v>
       </c>
       <c r="O45">
-        <v>3.98232126</v>
+        <v>3.96897408</v>
       </c>
       <c r="P45">
-        <v>10.76701674</v>
+        <v>10.73092992</v>
       </c>
       <c r="Q45">
-        <v>10.76701674</v>
+        <v>10.73092992</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1034977953531166</v>
+        <v>0.104348719637695</v>
       </c>
       <c r="T45">
-        <v>0.6912047210240698</v>
+        <v>0.7013985746910079</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.938703331009353</v>
+        <v>7.758278255304592</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07561948299710919</v>
+        <v>0.07571437264294191</v>
       </c>
       <c r="C46">
-        <v>61.85612705117542</v>
+        <v>60.84607763428485</v>
       </c>
       <c r="D46">
-        <v>93.00212705117542</v>
+        <v>92.91607763428485</v>
       </c>
       <c r="E46">
-        <v>-17.644</v>
+        <v>-16.72</v>
       </c>
       <c r="F46">
-        <v>40.65600000000001</v>
+        <v>41.58000000000001</v>
       </c>
       <c r="G46">
         <v>9.51</v>
@@ -5053,45 +5053,45 @@
         <v>16.875</v>
       </c>
       <c r="M46">
-        <v>2.175096</v>
+        <v>2.257794000000001</v>
       </c>
       <c r="N46">
-        <v>14.699904</v>
+        <v>14.617206</v>
       </c>
       <c r="O46">
-        <v>3.96897408</v>
+        <v>3.94664562</v>
       </c>
       <c r="P46">
-        <v>10.73092992</v>
+        <v>10.67056038</v>
       </c>
       <c r="Q46">
-        <v>10.73092992</v>
+        <v>10.67056038</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.104348719637695</v>
+        <v>0.1052305866235307</v>
       </c>
       <c r="T46">
-        <v>0.7013985746910079</v>
+        <v>0.7119631139458347</v>
       </c>
       <c r="U46">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V46">
         <v>0.27</v>
       </c>
       <c r="W46">
-        <v>0.039055</v>
+        <v>0.039639</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y46">
-        <v>7.758278255304592</v>
+        <v>7.474109684054434</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07571437264294191</v>
+        <v>0.07555230228877466</v>
       </c>
       <c r="C47">
-        <v>60.84607763428485</v>
+        <v>60.06914541294965</v>
       </c>
       <c r="D47">
-        <v>92.91607763428485</v>
+        <v>93.06314541294965</v>
       </c>
       <c r="E47">
-        <v>-16.72</v>
+        <v>-15.796</v>
       </c>
       <c r="F47">
-        <v>41.58000000000001</v>
+        <v>42.504</v>
       </c>
       <c r="G47">
         <v>9.51</v>
@@ -5135,28 +5135,28 @@
         <v>16.875</v>
       </c>
       <c r="M47">
-        <v>2.257794000000001</v>
+        <v>2.3079672</v>
       </c>
       <c r="N47">
-        <v>14.617206</v>
+        <v>14.5670328</v>
       </c>
       <c r="O47">
-        <v>3.94664562</v>
+        <v>3.933098856</v>
       </c>
       <c r="P47">
-        <v>10.67056038</v>
+        <v>10.633933944</v>
       </c>
       <c r="Q47">
-        <v>10.67056038</v>
+        <v>10.633933944</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1052305866235307</v>
+        <v>0.1061451153495827</v>
       </c>
       <c r="T47">
-        <v>0.7119631139458347</v>
+        <v>0.7229189324323219</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>7.474109684054434</v>
+        <v>7.311629038748904</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07555230228877466</v>
+        <v>0.07539023193460739</v>
       </c>
       <c r="C48">
-        <v>60.06914541294965</v>
+        <v>59.29267948809765</v>
       </c>
       <c r="D48">
-        <v>93.06314541294965</v>
+        <v>93.21067948809765</v>
       </c>
       <c r="E48">
-        <v>-15.796</v>
+        <v>-14.872</v>
       </c>
       <c r="F48">
-        <v>42.504</v>
+        <v>43.428</v>
       </c>
       <c r="G48">
         <v>9.51</v>
@@ -5217,28 +5217,28 @@
         <v>16.875</v>
       </c>
       <c r="M48">
-        <v>2.3079672</v>
+        <v>2.3581404</v>
       </c>
       <c r="N48">
-        <v>14.5670328</v>
+        <v>14.5168596</v>
       </c>
       <c r="O48">
-        <v>3.933098856</v>
+        <v>3.919552092</v>
       </c>
       <c r="P48">
-        <v>10.633933944</v>
+        <v>10.597307508</v>
       </c>
       <c r="Q48">
-        <v>10.633933944</v>
+        <v>10.597307508</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1061451153495827</v>
+        <v>0.1070941545935988</v>
       </c>
       <c r="T48">
-        <v>0.7229189324323219</v>
+        <v>0.7342881780315065</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>7.311629038748904</v>
+        <v>7.156062463456373</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07539023193460739</v>
+        <v>0.07522816158044013</v>
       </c>
       <c r="C49">
-        <v>59.29267948809765</v>
+        <v>58.51668208092563</v>
       </c>
       <c r="D49">
-        <v>93.21067948809765</v>
+        <v>93.35868208092563</v>
       </c>
       <c r="E49">
-        <v>-14.872</v>
+        <v>-13.948</v>
       </c>
       <c r="F49">
-        <v>43.428</v>
+        <v>44.352</v>
       </c>
       <c r="G49">
         <v>9.51</v>
@@ -5299,28 +5299,28 @@
         <v>16.875</v>
       </c>
       <c r="M49">
-        <v>2.3581404</v>
+        <v>2.4083136</v>
       </c>
       <c r="N49">
-        <v>14.5168596</v>
+        <v>14.4666864</v>
       </c>
       <c r="O49">
-        <v>3.919552092</v>
+        <v>3.906005328</v>
       </c>
       <c r="P49">
-        <v>10.597307508</v>
+        <v>10.560681072</v>
       </c>
       <c r="Q49">
-        <v>10.597307508</v>
+        <v>10.560681072</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1070941545935988</v>
+        <v>0.1080796953470002</v>
       </c>
       <c r="T49">
-        <v>0.7342881780315065</v>
+        <v>0.7460947023075829</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>7.156062463456373</v>
+        <v>7.006977828801033</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07522816158044013</v>
+        <v>0.07506609122627285</v>
       </c>
       <c r="C50">
-        <v>58.51668208092563</v>
+        <v>57.74115542676044</v>
       </c>
       <c r="D50">
-        <v>93.35868208092563</v>
+        <v>93.50715542676043</v>
       </c>
       <c r="E50">
-        <v>-13.948</v>
+        <v>-13.024</v>
       </c>
       <c r="F50">
-        <v>44.352</v>
+        <v>45.276</v>
       </c>
       <c r="G50">
         <v>9.51</v>
@@ -5381,28 +5381,28 @@
         <v>16.875</v>
       </c>
       <c r="M50">
-        <v>2.4083136</v>
+        <v>2.4584868</v>
       </c>
       <c r="N50">
-        <v>14.4666864</v>
+        <v>14.4165132</v>
       </c>
       <c r="O50">
-        <v>3.906005328</v>
+        <v>3.892458564</v>
       </c>
       <c r="P50">
-        <v>10.560681072</v>
+        <v>10.524054636</v>
       </c>
       <c r="Q50">
-        <v>10.560681072</v>
+        <v>10.524054636</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1080796953470002</v>
+        <v>0.1091038847573977</v>
       </c>
       <c r="T50">
-        <v>0.7460947023075829</v>
+        <v>0.7583642275356622</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>7.006977828801033</v>
+        <v>6.863978281274481</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07506609122627285</v>
+        <v>0.07490402087210558</v>
       </c>
       <c r="C51">
-        <v>57.74115542676044</v>
+        <v>56.96610177517125</v>
       </c>
       <c r="D51">
-        <v>93.50715542676043</v>
+        <v>93.65610177517125</v>
       </c>
       <c r="E51">
-        <v>-13.024</v>
+        <v>-12.1</v>
       </c>
       <c r="F51">
-        <v>45.276</v>
+        <v>46.2</v>
       </c>
       <c r="G51">
         <v>9.51</v>
@@ -5463,28 +5463,28 @@
         <v>16.875</v>
       </c>
       <c r="M51">
-        <v>2.4584868</v>
+        <v>2.50866</v>
       </c>
       <c r="N51">
-        <v>14.4165132</v>
+        <v>14.36634</v>
       </c>
       <c r="O51">
-        <v>3.892458564</v>
+        <v>3.8789118</v>
       </c>
       <c r="P51">
-        <v>10.524054636</v>
+        <v>10.4874282</v>
       </c>
       <c r="Q51">
-        <v>10.524054636</v>
+        <v>10.4874282</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1091038847573977</v>
+        <v>0.1101690417442112</v>
       </c>
       <c r="T51">
-        <v>0.7583642275356622</v>
+        <v>0.7711245337728648</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.863978281274481</v>
+        <v>6.726698715648991</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07490402087210558</v>
+        <v>0.07474195051793833</v>
       </c>
       <c r="C52">
-        <v>56.96610177517125</v>
+        <v>56.19152339008352</v>
       </c>
       <c r="D52">
-        <v>93.65610177517125</v>
+        <v>93.80552339008352</v>
       </c>
       <c r="E52">
-        <v>-12.1</v>
+        <v>-11.176</v>
       </c>
       <c r="F52">
-        <v>46.2</v>
+        <v>47.124</v>
       </c>
       <c r="G52">
         <v>9.51</v>
@@ -5545,28 +5545,28 @@
         <v>16.875</v>
       </c>
       <c r="M52">
-        <v>2.50866</v>
+        <v>2.5588332</v>
       </c>
       <c r="N52">
-        <v>14.36634</v>
+        <v>14.3161668</v>
       </c>
       <c r="O52">
-        <v>3.8789118</v>
+        <v>3.865365036</v>
       </c>
       <c r="P52">
-        <v>10.4874282</v>
+        <v>10.450801764</v>
       </c>
       <c r="Q52">
-        <v>10.4874282</v>
+        <v>10.450801764</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1101690417442112</v>
+        <v>0.1112776745264047</v>
       </c>
       <c r="T52">
-        <v>0.7711245337728648</v>
+        <v>0.7844056688360758</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>6.726698715648991</v>
+        <v>6.594802662400972</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07474195051793833</v>
+        <v>0.07457988016377105</v>
       </c>
       <c r="C53">
-        <v>56.19152339008352</v>
+        <v>55.41742254989346</v>
       </c>
       <c r="D53">
-        <v>93.80552339008352</v>
+        <v>93.95542254989346</v>
       </c>
       <c r="E53">
-        <v>-11.176</v>
+        <v>-10.252</v>
       </c>
       <c r="F53">
-        <v>47.124</v>
+        <v>48.048</v>
       </c>
       <c r="G53">
         <v>9.51</v>
@@ -5627,28 +5627,28 @@
         <v>16.875</v>
       </c>
       <c r="M53">
-        <v>2.5588332</v>
+        <v>2.6090064</v>
       </c>
       <c r="N53">
-        <v>14.3161668</v>
+        <v>14.2659936</v>
       </c>
       <c r="O53">
-        <v>3.865365036</v>
+        <v>3.851818272</v>
       </c>
       <c r="P53">
-        <v>10.450801764</v>
+        <v>10.414175328</v>
       </c>
       <c r="Q53">
-        <v>10.450801764</v>
+        <v>10.414175328</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1112776745264047</v>
+        <v>0.1124325003411897</v>
       </c>
       <c r="T53">
-        <v>0.7844056688360758</v>
+        <v>0.7982401845269204</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>6.594802662400972</v>
+        <v>6.467979534277877</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07457988016377105</v>
+        <v>0.07441780980960379</v>
       </c>
       <c r="C54">
-        <v>55.41742254989346</v>
+        <v>54.64380154758382</v>
       </c>
       <c r="D54">
-        <v>93.95542254989346</v>
+        <v>94.10580154758382</v>
       </c>
       <c r="E54">
-        <v>-10.252</v>
+        <v>-9.327999999999996</v>
       </c>
       <c r="F54">
-        <v>48.048</v>
+        <v>48.97200000000001</v>
       </c>
       <c r="G54">
         <v>9.51</v>
@@ -5709,28 +5709,28 @@
         <v>16.875</v>
       </c>
       <c r="M54">
-        <v>2.6090064</v>
+        <v>2.6591796</v>
       </c>
       <c r="N54">
-        <v>14.2659936</v>
+        <v>14.2158204</v>
       </c>
       <c r="O54">
-        <v>3.851818272</v>
+        <v>3.838271508</v>
       </c>
       <c r="P54">
-        <v>10.414175328</v>
+        <v>10.377548892</v>
       </c>
       <c r="Q54">
-        <v>10.414175328</v>
+        <v>10.377548892</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1124325003411897</v>
+        <v>0.1136364676800081</v>
       </c>
       <c r="T54">
-        <v>0.7982401845269204</v>
+        <v>0.8126634030131201</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>6.467979534277877</v>
+        <v>6.34594218457452</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07441780980960379</v>
+        <v>0.07425573945543652</v>
       </c>
       <c r="C55">
-        <v>54.64380154758382</v>
+        <v>53.87066269084101</v>
       </c>
       <c r="D55">
-        <v>94.10580154758382</v>
+        <v>94.25666269084101</v>
       </c>
       <c r="E55">
-        <v>-9.327999999999996</v>
+        <v>-8.403999999999996</v>
       </c>
       <c r="F55">
-        <v>48.97200000000001</v>
+        <v>49.89600000000001</v>
       </c>
       <c r="G55">
         <v>9.51</v>
@@ -5791,28 +5791,28 @@
         <v>16.875</v>
       </c>
       <c r="M55">
-        <v>2.6591796</v>
+        <v>2.7093528</v>
       </c>
       <c r="N55">
-        <v>14.2158204</v>
+        <v>14.1656472</v>
       </c>
       <c r="O55">
-        <v>3.838271508</v>
+        <v>3.824724744</v>
       </c>
       <c r="P55">
-        <v>10.377548892</v>
+        <v>10.340922456</v>
       </c>
       <c r="Q55">
-        <v>10.377548892</v>
+        <v>10.340922456</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1136364676800081</v>
+        <v>0.114892781424862</v>
       </c>
       <c r="T55">
-        <v>0.8126634030131201</v>
+        <v>0.8277137179552414</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>6.34594218457452</v>
+        <v>6.228424736712028</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07425573945543652</v>
+        <v>0.07409366910126926</v>
       </c>
       <c r="C56">
-        <v>53.87066269084101</v>
+        <v>53.09800830217293</v>
       </c>
       <c r="D56">
-        <v>94.25666269084101</v>
+        <v>94.40800830217293</v>
       </c>
       <c r="E56">
-        <v>-8.403999999999996</v>
+        <v>-7.479999999999997</v>
       </c>
       <c r="F56">
-        <v>49.89600000000001</v>
+        <v>50.82000000000001</v>
       </c>
       <c r="G56">
         <v>9.51</v>
@@ -5873,28 +5873,28 @@
         <v>16.875</v>
       </c>
       <c r="M56">
-        <v>2.7093528</v>
+        <v>2.759526000000001</v>
       </c>
       <c r="N56">
-        <v>14.1656472</v>
+        <v>14.115474</v>
       </c>
       <c r="O56">
-        <v>3.824724744</v>
+        <v>3.81117798</v>
       </c>
       <c r="P56">
-        <v>10.340922456</v>
+        <v>10.30429602</v>
       </c>
       <c r="Q56">
-        <v>10.340922456</v>
+        <v>10.30429602</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.114892781424862</v>
+        <v>0.1162049313361539</v>
       </c>
       <c r="T56">
-        <v>0.8277137179552414</v>
+        <v>0.8434329357836795</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>6.228424736712028</v>
+        <v>6.115180650589991</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07409366910126926</v>
+        <v>0.07434039874710199</v>
       </c>
       <c r="C57">
-        <v>53.09800830217293</v>
+        <v>51.94379836789259</v>
       </c>
       <c r="D57">
-        <v>94.40800830217293</v>
+        <v>94.17779836789259</v>
       </c>
       <c r="E57">
-        <v>-7.479999999999997</v>
+        <v>-6.555999999999997</v>
       </c>
       <c r="F57">
-        <v>50.82000000000001</v>
+        <v>51.74400000000001</v>
       </c>
       <c r="G57">
         <v>9.51</v>
@@ -5955,45 +5955,45 @@
         <v>16.875</v>
       </c>
       <c r="M57">
-        <v>2.759526000000001</v>
+        <v>2.861443200000001</v>
       </c>
       <c r="N57">
-        <v>14.115474</v>
+        <v>14.0135568</v>
       </c>
       <c r="O57">
-        <v>3.81117798</v>
+        <v>3.783660336</v>
       </c>
       <c r="P57">
-        <v>10.30429602</v>
+        <v>10.229896464</v>
       </c>
       <c r="Q57">
-        <v>10.30429602</v>
+        <v>10.229896464</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1162049313361539</v>
+        <v>0.1175767244252318</v>
       </c>
       <c r="T57">
-        <v>0.8434329357836795</v>
+        <v>0.85986666351341</v>
       </c>
       <c r="U57">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V57">
         <v>0.27</v>
       </c>
       <c r="W57">
-        <v>0.039639</v>
+        <v>0.040369</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y57">
-        <v>6.115180650589991</v>
+        <v>5.897373744829181</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07434039874710199</v>
+        <v>0.07418562839293473</v>
       </c>
       <c r="C58">
-        <v>51.94379836789259</v>
+        <v>51.16407467286177</v>
       </c>
       <c r="D58">
-        <v>94.17779836789259</v>
+        <v>94.32207467286177</v>
       </c>
       <c r="E58">
-        <v>-6.555999999999997</v>
+        <v>-5.631999999999998</v>
       </c>
       <c r="F58">
-        <v>51.74400000000001</v>
+        <v>52.66800000000001</v>
       </c>
       <c r="G58">
         <v>9.51</v>
@@ -6037,28 +6037,28 @@
         <v>16.875</v>
       </c>
       <c r="M58">
-        <v>2.861443200000001</v>
+        <v>2.912540400000001</v>
       </c>
       <c r="N58">
-        <v>14.0135568</v>
+        <v>13.9624596</v>
       </c>
       <c r="O58">
-        <v>3.783660336</v>
+        <v>3.769864092</v>
       </c>
       <c r="P58">
-        <v>10.229896464</v>
+        <v>10.192595508</v>
       </c>
       <c r="Q58">
-        <v>10.229896464</v>
+        <v>10.192595508</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1175767244252318</v>
+        <v>0.1190123218440343</v>
       </c>
       <c r="T58">
-        <v>0.85986666351341</v>
+        <v>0.8770647506724305</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.897373744829181</v>
+        <v>5.793911047551476</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07418562839293473</v>
+        <v>0.07403085803876747</v>
       </c>
       <c r="C59">
-        <v>51.16407467286177</v>
+        <v>50.38479370616271</v>
       </c>
       <c r="D59">
-        <v>94.32207467286177</v>
+        <v>94.46679370616272</v>
       </c>
       <c r="E59">
-        <v>-5.631999999999998</v>
+        <v>-4.707999999999991</v>
       </c>
       <c r="F59">
-        <v>52.66800000000001</v>
+        <v>53.59200000000001</v>
       </c>
       <c r="G59">
         <v>9.51</v>
@@ -6119,28 +6119,28 @@
         <v>16.875</v>
       </c>
       <c r="M59">
-        <v>2.912540400000001</v>
+        <v>2.963637600000001</v>
       </c>
       <c r="N59">
-        <v>13.9624596</v>
+        <v>13.9113624</v>
       </c>
       <c r="O59">
-        <v>3.769864092</v>
+        <v>3.756067848</v>
       </c>
       <c r="P59">
-        <v>10.192595508</v>
+        <v>10.155294552</v>
       </c>
       <c r="Q59">
-        <v>10.192595508</v>
+        <v>10.155294552</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1190123218440343</v>
+        <v>0.1205162810446845</v>
       </c>
       <c r="T59">
-        <v>0.8770647506724305</v>
+        <v>0.8950817943628329</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.793911047551476</v>
+        <v>5.694016029490244</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07403085803876747</v>
+        <v>0.07387608768460019</v>
       </c>
       <c r="C60">
-        <v>50.38479370616272</v>
+        <v>49.60595750877064</v>
       </c>
       <c r="D60">
-        <v>94.46679370616272</v>
+        <v>94.61195750877063</v>
       </c>
       <c r="E60">
-        <v>-4.708000000000006</v>
+        <v>-3.784000000000006</v>
       </c>
       <c r="F60">
-        <v>53.592</v>
+        <v>54.516</v>
       </c>
       <c r="G60">
         <v>9.51</v>
@@ -6201,28 +6201,28 @@
         <v>16.875</v>
       </c>
       <c r="M60">
-        <v>2.9636376</v>
+        <v>3.0147348</v>
       </c>
       <c r="N60">
-        <v>13.9113624</v>
+        <v>13.8602652</v>
       </c>
       <c r="O60">
-        <v>3.756067848</v>
+        <v>3.742271604</v>
       </c>
       <c r="P60">
-        <v>10.155294552</v>
+        <v>10.117993596</v>
       </c>
       <c r="Q60">
-        <v>10.155294552</v>
+        <v>10.117993596</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1205162810446844</v>
+        <v>0.122093604108781</v>
       </c>
       <c r="T60">
-        <v>0.8950817943628325</v>
+        <v>0.9139777182332545</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.694016029490245</v>
+        <v>5.597507283227699</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07387608768460019</v>
+        <v>0.07372131733043293</v>
       </c>
       <c r="C61">
-        <v>49.60595750877064</v>
+        <v>48.82756813422518</v>
       </c>
       <c r="D61">
-        <v>94.61195750877063</v>
+        <v>94.75756813422518</v>
       </c>
       <c r="E61">
-        <v>-3.784000000000006</v>
+        <v>-2.859999999999999</v>
       </c>
       <c r="F61">
-        <v>54.516</v>
+        <v>55.44</v>
       </c>
       <c r="G61">
         <v>9.51</v>
@@ -6283,28 +6283,28 @@
         <v>16.875</v>
       </c>
       <c r="M61">
-        <v>3.0147348</v>
+        <v>3.065832</v>
       </c>
       <c r="N61">
-        <v>13.8602652</v>
+        <v>13.809168</v>
       </c>
       <c r="O61">
-        <v>3.742271604</v>
+        <v>3.72847536</v>
       </c>
       <c r="P61">
-        <v>10.117993596</v>
+        <v>10.08069264</v>
       </c>
       <c r="Q61">
-        <v>10.117993596</v>
+        <v>10.08069264</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.122093604108781</v>
+        <v>0.1237497933260823</v>
       </c>
       <c r="T61">
-        <v>0.9139777182332545</v>
+        <v>0.9338184382971975</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.597507283227699</v>
+        <v>5.504215495173903</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07372131733043293</v>
+        <v>0.07356654697626566</v>
       </c>
       <c r="C62">
-        <v>48.82756813422518</v>
+        <v>48.04962764872742</v>
       </c>
       <c r="D62">
-        <v>94.75756813422518</v>
+        <v>94.90362764872742</v>
       </c>
       <c r="E62">
-        <v>-2.859999999999999</v>
+        <v>-1.936</v>
       </c>
       <c r="F62">
-        <v>55.44</v>
+        <v>56.364</v>
       </c>
       <c r="G62">
         <v>9.51</v>
@@ -6365,28 +6365,28 @@
         <v>16.875</v>
       </c>
       <c r="M62">
-        <v>3.065832</v>
+        <v>3.1169292</v>
       </c>
       <c r="N62">
-        <v>13.809168</v>
+        <v>13.7580708</v>
       </c>
       <c r="O62">
-        <v>3.72847536</v>
+        <v>3.714679116</v>
       </c>
       <c r="P62">
-        <v>10.08069264</v>
+        <v>10.043391684</v>
       </c>
       <c r="Q62">
-        <v>10.08069264</v>
+        <v>10.043391684</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1237497933260823</v>
+        <v>0.1254909153237581</v>
       </c>
       <c r="T62">
-        <v>0.9338184382971975</v>
+        <v>0.9546766311849326</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.504215495173903</v>
+        <v>5.413982454269413</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07356654697626566</v>
+        <v>0.07341177662209838</v>
       </c>
       <c r="C63">
-        <v>48.04962764872742</v>
+        <v>47.27213813123745</v>
       </c>
       <c r="D63">
-        <v>94.90362764872742</v>
+        <v>95.05013813123745</v>
       </c>
       <c r="E63">
-        <v>-1.936</v>
+        <v>-1.012</v>
       </c>
       <c r="F63">
-        <v>56.364</v>
+        <v>57.288</v>
       </c>
       <c r="G63">
         <v>9.51</v>
@@ -6447,28 +6447,28 @@
         <v>16.875</v>
       </c>
       <c r="M63">
-        <v>3.1169292</v>
+        <v>3.1680264</v>
       </c>
       <c r="N63">
-        <v>13.7580708</v>
+        <v>13.7069736</v>
       </c>
       <c r="O63">
-        <v>3.714679116</v>
+        <v>3.700882872</v>
       </c>
       <c r="P63">
-        <v>10.043391684</v>
+        <v>10.006090728</v>
       </c>
       <c r="Q63">
-        <v>10.043391684</v>
+        <v>10.006090728</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1254909153237581</v>
+        <v>0.1273236753213116</v>
       </c>
       <c r="T63">
-        <v>0.9546766311849326</v>
+        <v>0.9766326236983378</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.413982454269413</v>
+        <v>5.326660156619906</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07341177662209838</v>
+        <v>0.07325700626793114</v>
       </c>
       <c r="C64">
-        <v>47.27213813123745</v>
+        <v>46.49510167357296</v>
       </c>
       <c r="D64">
-        <v>95.05013813123745</v>
+        <v>95.19710167357296</v>
       </c>
       <c r="E64">
-        <v>-1.012</v>
+        <v>-0.08800000000000097</v>
       </c>
       <c r="F64">
-        <v>57.288</v>
+        <v>58.212</v>
       </c>
       <c r="G64">
         <v>9.51</v>
@@ -6529,28 +6529,28 @@
         <v>16.875</v>
       </c>
       <c r="M64">
-        <v>3.1680264</v>
+        <v>3.2191236</v>
       </c>
       <c r="N64">
-        <v>13.7069736</v>
+        <v>13.6558764</v>
       </c>
       <c r="O64">
-        <v>3.700882872</v>
+        <v>3.687086628</v>
       </c>
       <c r="P64">
-        <v>10.006090728</v>
+        <v>9.968789772000001</v>
       </c>
       <c r="Q64">
-        <v>10.006090728</v>
+        <v>9.968789772000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1273236753213116</v>
+        <v>0.1292555034268409</v>
       </c>
       <c r="T64">
-        <v>0.9766326236983378</v>
+        <v>0.999775426617873</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.326660156619906</v>
+        <v>5.242109995403718</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07325700626793114</v>
+        <v>0.07310223591376387</v>
       </c>
       <c r="C65">
-        <v>46.49510167357296</v>
+        <v>45.71852038050901</v>
       </c>
       <c r="D65">
-        <v>95.19710167357296</v>
+        <v>95.34452038050901</v>
       </c>
       <c r="E65">
-        <v>-0.08800000000000097</v>
+        <v>0.8359999999999985</v>
       </c>
       <c r="F65">
-        <v>58.212</v>
+        <v>59.136</v>
       </c>
       <c r="G65">
         <v>9.51</v>
@@ -6611,28 +6611,28 @@
         <v>16.875</v>
       </c>
       <c r="M65">
-        <v>3.2191236</v>
+        <v>3.2702208</v>
       </c>
       <c r="N65">
-        <v>13.6558764</v>
+        <v>13.6047792</v>
       </c>
       <c r="O65">
-        <v>3.687086628</v>
+        <v>3.673290384</v>
       </c>
       <c r="P65">
-        <v>9.968789772000001</v>
+        <v>9.931488816</v>
       </c>
       <c r="Q65">
-        <v>9.968789772000001</v>
+        <v>9.931488816</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1292555034268409</v>
+        <v>0.1312946553160108</v>
       </c>
       <c r="T65">
-        <v>0.999775426617873</v>
+        <v>1.024203940810716</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.242109995403718</v>
+        <v>5.160202026725535</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07310223591376387</v>
+        <v>0.07294746555959659</v>
       </c>
       <c r="C66">
-        <v>45.71852038050901</v>
+        <v>44.94239636987837</v>
       </c>
       <c r="D66">
-        <v>95.34452038050901</v>
+        <v>95.49239636987836</v>
       </c>
       <c r="E66">
-        <v>0.8359999999999985</v>
+        <v>1.759999999999998</v>
       </c>
       <c r="F66">
-        <v>59.136</v>
+        <v>60.06</v>
       </c>
       <c r="G66">
         <v>9.51</v>
@@ -6693,28 +6693,28 @@
         <v>16.875</v>
       </c>
       <c r="M66">
-        <v>3.2702208</v>
+        <v>3.321318</v>
       </c>
       <c r="N66">
-        <v>13.6047792</v>
+        <v>13.553682</v>
       </c>
       <c r="O66">
-        <v>3.673290384</v>
+        <v>3.659494140000001</v>
       </c>
       <c r="P66">
-        <v>9.931488816</v>
+        <v>9.894187859999999</v>
       </c>
       <c r="Q66">
-        <v>9.931488816</v>
+        <v>9.894187859999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1312946553160108</v>
+        <v>0.133450330170276</v>
       </c>
       <c r="T66">
-        <v>1.024203940810716</v>
+        <v>1.050028370100293</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.160202026725535</v>
+        <v>5.08081430323745</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07294746555959659</v>
+        <v>0.07279269520542933</v>
       </c>
       <c r="C67">
-        <v>44.94239636987837</v>
+        <v>44.16673177267288</v>
       </c>
       <c r="D67">
-        <v>95.49239636987836</v>
+        <v>95.64073177267288</v>
       </c>
       <c r="E67">
-        <v>1.759999999999998</v>
+        <v>2.684000000000005</v>
       </c>
       <c r="F67">
-        <v>60.06</v>
+        <v>60.98400000000001</v>
       </c>
       <c r="G67">
         <v>9.51</v>
@@ -6775,28 +6775,28 @@
         <v>16.875</v>
       </c>
       <c r="M67">
-        <v>3.321318</v>
+        <v>3.372415200000001</v>
       </c>
       <c r="N67">
-        <v>13.553682</v>
+        <v>13.5025848</v>
       </c>
       <c r="O67">
-        <v>3.659494140000001</v>
+        <v>3.645697896</v>
       </c>
       <c r="P67">
-        <v>9.894187859999999</v>
+        <v>9.856886904</v>
       </c>
       <c r="Q67">
-        <v>9.894187859999999</v>
+        <v>9.856886904</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.133450330170276</v>
+        <v>0.1357328094277333</v>
       </c>
       <c r="T67">
-        <v>1.050028370100293</v>
+        <v>1.077371883465726</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.08081430323745</v>
+        <v>5.003832268339911</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07279269520542933</v>
+        <v>0.07263792485126207</v>
       </c>
       <c r="C68">
-        <v>44.16673177267288</v>
+        <v>43.39152873314594</v>
       </c>
       <c r="D68">
-        <v>95.64073177267288</v>
+        <v>95.78952873314594</v>
       </c>
       <c r="E68">
-        <v>2.684000000000005</v>
+        <v>3.608000000000004</v>
       </c>
       <c r="F68">
-        <v>60.98400000000001</v>
+        <v>61.90800000000001</v>
       </c>
       <c r="G68">
         <v>9.51</v>
@@ -6857,28 +6857,28 @@
         <v>16.875</v>
       </c>
       <c r="M68">
-        <v>3.372415200000001</v>
+        <v>3.423512400000001</v>
       </c>
       <c r="N68">
-        <v>13.5025848</v>
+        <v>13.4514876</v>
       </c>
       <c r="O68">
-        <v>3.645697896</v>
+        <v>3.631901652</v>
       </c>
       <c r="P68">
-        <v>9.856886904</v>
+        <v>9.819585948</v>
       </c>
       <c r="Q68">
-        <v>9.856886904</v>
+        <v>9.819585948</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1357328094277333</v>
+        <v>0.1381536207614002</v>
       </c>
       <c r="T68">
-        <v>1.077371883465726</v>
+        <v>1.106372579459369</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.003832268339911</v>
+        <v>4.929148204633346</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07263792485126207</v>
+        <v>0.0724831544970948</v>
       </c>
       <c r="C69">
-        <v>43.39152873314594</v>
+        <v>42.61678940891578</v>
       </c>
       <c r="D69">
-        <v>95.78952873314594</v>
+        <v>95.93878940891578</v>
       </c>
       <c r="E69">
-        <v>3.608000000000004</v>
+        <v>4.532000000000004</v>
       </c>
       <c r="F69">
-        <v>61.90800000000001</v>
+        <v>62.83200000000001</v>
       </c>
       <c r="G69">
         <v>9.51</v>
@@ -6939,28 +6939,28 @@
         <v>16.875</v>
       </c>
       <c r="M69">
-        <v>3.423512400000001</v>
+        <v>3.4746096</v>
       </c>
       <c r="N69">
-        <v>13.4514876</v>
+        <v>13.4003904</v>
       </c>
       <c r="O69">
-        <v>3.631901652</v>
+        <v>3.618105408</v>
       </c>
       <c r="P69">
-        <v>9.819585948</v>
+        <v>9.782284991999999</v>
       </c>
       <c r="Q69">
-        <v>9.819585948</v>
+        <v>9.782284991999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1381536207614002</v>
+        <v>0.1407257328034213</v>
       </c>
       <c r="T69">
-        <v>1.106372579459369</v>
+        <v>1.137185818952614</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.929148204633346</v>
+        <v>4.856660731035797</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.0724831544970948</v>
+        <v>0.07232838414292754</v>
       </c>
       <c r="C70">
-        <v>42.61678940891578</v>
+        <v>41.84251597106977</v>
       </c>
       <c r="D70">
-        <v>95.93878940891578</v>
+        <v>96.08851597106977</v>
       </c>
       <c r="E70">
-        <v>4.532000000000004</v>
+        <v>5.456000000000003</v>
       </c>
       <c r="F70">
-        <v>62.83200000000001</v>
+        <v>63.75600000000001</v>
       </c>
       <c r="G70">
         <v>9.51</v>
@@ -7021,28 +7021,28 @@
         <v>16.875</v>
       </c>
       <c r="M70">
-        <v>3.4746096</v>
+        <v>3.5257068</v>
       </c>
       <c r="N70">
-        <v>13.4003904</v>
+        <v>13.3492932</v>
       </c>
       <c r="O70">
-        <v>3.618105408</v>
+        <v>3.604309164</v>
       </c>
       <c r="P70">
-        <v>9.782284991999999</v>
+        <v>9.744984036</v>
       </c>
       <c r="Q70">
-        <v>9.782284991999999</v>
+        <v>9.744984036</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1407257328034213</v>
+        <v>0.1434637875578308</v>
       </c>
       <c r="T70">
-        <v>1.137185818952614</v>
+        <v>1.169987009380907</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.856660731035797</v>
+        <v>4.786274343629481</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07232838414292754</v>
+        <v>0.07217361378876028</v>
       </c>
       <c r="C71">
-        <v>41.84251597106977</v>
+        <v>41.06871060426961</v>
       </c>
       <c r="D71">
-        <v>96.08851597106977</v>
+        <v>96.23871060426961</v>
       </c>
       <c r="E71">
-        <v>5.456000000000003</v>
+        <v>6.380000000000003</v>
       </c>
       <c r="F71">
-        <v>63.75600000000001</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="G71">
         <v>9.51</v>
@@ -7103,28 +7103,28 @@
         <v>16.875</v>
       </c>
       <c r="M71">
-        <v>3.5257068</v>
+        <v>3.576804000000001</v>
       </c>
       <c r="N71">
-        <v>13.3492932</v>
+        <v>13.298196</v>
       </c>
       <c r="O71">
-        <v>3.604309164</v>
+        <v>3.59051292</v>
       </c>
       <c r="P71">
-        <v>9.744984036</v>
+        <v>9.707683079999999</v>
       </c>
       <c r="Q71">
-        <v>9.744984036</v>
+        <v>9.707683079999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1434637875578308</v>
+        <v>0.1463843792958676</v>
       </c>
       <c r="T71">
-        <v>1.169987009380907</v>
+        <v>1.204974945837753</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.786274343629481</v>
+        <v>4.717898995863345</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07217361378876028</v>
+        <v>0.072018843434593</v>
       </c>
       <c r="C72">
-        <v>41.06871060426961</v>
+        <v>40.29537550685771</v>
       </c>
       <c r="D72">
-        <v>96.23871060426961</v>
+        <v>96.38937550685772</v>
       </c>
       <c r="E72">
-        <v>6.380000000000003</v>
+        <v>7.304000000000009</v>
       </c>
       <c r="F72">
-        <v>64.68000000000001</v>
+        <v>65.60400000000001</v>
       </c>
       <c r="G72">
         <v>9.51</v>
@@ -7185,28 +7185,28 @@
         <v>16.875</v>
       </c>
       <c r="M72">
-        <v>3.576804000000001</v>
+        <v>3.627901200000001</v>
       </c>
       <c r="N72">
-        <v>13.298196</v>
+        <v>13.2470988</v>
       </c>
       <c r="O72">
-        <v>3.59051292</v>
+        <v>3.576716676</v>
       </c>
       <c r="P72">
-        <v>9.707683079999999</v>
+        <v>9.670382124</v>
       </c>
       <c r="Q72">
-        <v>9.707683079999999</v>
+        <v>9.670382124</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1463843792958676</v>
+        <v>0.149506391153769</v>
       </c>
       <c r="T72">
-        <v>1.204974945837753</v>
+        <v>1.242375843429553</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.717898995863345</v>
+        <v>4.651449714231466</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07201884343459301</v>
+        <v>0.07186407308042575</v>
       </c>
       <c r="C73">
-        <v>40.29537550685771</v>
+        <v>39.52251289096429</v>
       </c>
       <c r="D73">
-        <v>96.3893755068577</v>
+        <v>96.54051289096429</v>
       </c>
       <c r="E73">
-        <v>7.303999999999995</v>
+        <v>8.228000000000002</v>
       </c>
       <c r="F73">
-        <v>65.604</v>
+        <v>66.52800000000001</v>
       </c>
       <c r="G73">
         <v>9.51</v>
@@ -7267,28 +7267,28 @@
         <v>16.875</v>
       </c>
       <c r="M73">
-        <v>3.6279012</v>
+        <v>3.678998400000001</v>
       </c>
       <c r="N73">
-        <v>13.2470988</v>
+        <v>13.1960016</v>
       </c>
       <c r="O73">
-        <v>3.576716676</v>
+        <v>3.562920432</v>
       </c>
       <c r="P73">
-        <v>9.670382124</v>
+        <v>9.633081167999999</v>
       </c>
       <c r="Q73">
-        <v>9.670382124</v>
+        <v>9.633081167999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.149506391153769</v>
+        <v>0.1528514038586634</v>
       </c>
       <c r="T73">
-        <v>1.242375843429553</v>
+        <v>1.282448233706482</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.651449714231468</v>
+        <v>4.586846245978252</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07186407308042575</v>
+        <v>0.07170930272625847</v>
       </c>
       <c r="C74">
-        <v>39.52251289096429</v>
+        <v>38.75012498261584</v>
       </c>
       <c r="D74">
-        <v>96.54051289096429</v>
+        <v>96.69212498261584</v>
       </c>
       <c r="E74">
-        <v>8.228000000000002</v>
+        <v>9.151999999999994</v>
       </c>
       <c r="F74">
-        <v>66.52800000000001</v>
+        <v>67.452</v>
       </c>
       <c r="G74">
         <v>9.51</v>
@@ -7349,28 +7349,28 @@
         <v>16.875</v>
       </c>
       <c r="M74">
-        <v>3.678998400000001</v>
+        <v>3.7300956</v>
       </c>
       <c r="N74">
-        <v>13.1960016</v>
+        <v>13.1449044</v>
       </c>
       <c r="O74">
-        <v>3.562920432</v>
+        <v>3.549124188</v>
       </c>
       <c r="P74">
-        <v>9.633081167999999</v>
+        <v>9.595780211999999</v>
       </c>
       <c r="Q74">
-        <v>9.633081167999999</v>
+        <v>9.595780211999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1528514038586634</v>
+        <v>0.1564441952824387</v>
       </c>
       <c r="T74">
-        <v>1.282448233706482</v>
+        <v>1.32548894918911</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.586846245978252</v>
+        <v>4.524012735759372</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07170930272625847</v>
+        <v>0.0729050323720912</v>
       </c>
       <c r="C75">
-        <v>38.75012498261584</v>
+        <v>36.66701949304087</v>
       </c>
       <c r="D75">
-        <v>96.69212498261584</v>
+        <v>95.53301949304087</v>
       </c>
       <c r="E75">
-        <v>9.151999999999994</v>
+        <v>10.076</v>
       </c>
       <c r="F75">
-        <v>67.452</v>
+        <v>68.376</v>
       </c>
       <c r="G75">
         <v>9.51</v>
@@ -7431,45 +7431,45 @@
         <v>16.875</v>
       </c>
       <c r="M75">
-        <v>3.7300956</v>
+        <v>3.952132800000001</v>
       </c>
       <c r="N75">
-        <v>13.1449044</v>
+        <v>12.9228672</v>
       </c>
       <c r="O75">
-        <v>3.549124188</v>
+        <v>3.489174144</v>
       </c>
       <c r="P75">
-        <v>9.595780211999999</v>
+        <v>9.433693055999999</v>
       </c>
       <c r="Q75">
-        <v>9.595780211999999</v>
+        <v>9.433693055999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1564441952824387</v>
+        <v>0.1603133552772739</v>
       </c>
       <c r="T75">
-        <v>1.32548894918911</v>
+        <v>1.371840488939632</v>
       </c>
       <c r="U75">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V75">
         <v>0.27</v>
       </c>
       <c r="W75">
-        <v>0.040369</v>
+        <v>0.042194</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y75">
-        <v>4.524012735759372</v>
+        <v>4.269846397874079</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.0729050323720912</v>
+        <v>0.07276851201792395</v>
       </c>
       <c r="C76">
-        <v>36.66701949304087</v>
+        <v>35.87395112514375</v>
       </c>
       <c r="D76">
-        <v>95.53301949304087</v>
+        <v>95.66395112514375</v>
       </c>
       <c r="E76">
-        <v>10.076</v>
+        <v>11.00000000000001</v>
       </c>
       <c r="F76">
-        <v>68.376</v>
+        <v>69.30000000000001</v>
       </c>
       <c r="G76">
         <v>9.51</v>
@@ -7513,28 +7513,28 @@
         <v>16.875</v>
       </c>
       <c r="M76">
-        <v>3.952132800000001</v>
+        <v>4.005540000000001</v>
       </c>
       <c r="N76">
-        <v>12.9228672</v>
+        <v>12.86946</v>
       </c>
       <c r="O76">
-        <v>3.489174144</v>
+        <v>3.4747542</v>
       </c>
       <c r="P76">
-        <v>9.433693055999999</v>
+        <v>9.394705800000001</v>
       </c>
       <c r="Q76">
-        <v>9.433693055999999</v>
+        <v>9.394705800000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1603133552772739</v>
+        <v>0.1644920480716958</v>
       </c>
       <c r="T76">
-        <v>1.371840488939632</v>
+        <v>1.421900151870196</v>
       </c>
       <c r="U76">
         <v>0.0578</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.269846397874079</v>
+        <v>4.212915112569091</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07276851201792395</v>
+        <v>0.07263199166375668</v>
       </c>
       <c r="C77">
-        <v>35.87395112514375</v>
+        <v>35.08124214334961</v>
       </c>
       <c r="D77">
-        <v>95.66395112514375</v>
+        <v>95.79524214334961</v>
       </c>
       <c r="E77">
-        <v>11.00000000000001</v>
+        <v>11.924</v>
       </c>
       <c r="F77">
-        <v>69.30000000000001</v>
+        <v>70.224</v>
       </c>
       <c r="G77">
         <v>9.51</v>
@@ -7595,28 +7595,28 @@
         <v>16.875</v>
       </c>
       <c r="M77">
-        <v>4.005540000000001</v>
+        <v>4.0589472</v>
       </c>
       <c r="N77">
-        <v>12.86946</v>
+        <v>12.8160528</v>
       </c>
       <c r="O77">
-        <v>3.4747542</v>
+        <v>3.460334256</v>
       </c>
       <c r="P77">
-        <v>9.394705800000001</v>
+        <v>9.355718543999998</v>
       </c>
       <c r="Q77">
-        <v>9.394705800000001</v>
+        <v>9.355718543999998</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1644920480716958</v>
+        <v>0.1690189652656528</v>
       </c>
       <c r="T77">
-        <v>1.421900151870196</v>
+        <v>1.476131453378307</v>
       </c>
       <c r="U77">
         <v>0.0578</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.212915112569091</v>
+        <v>4.157482018982655</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07263199166375668</v>
+        <v>0.07249547130958942</v>
       </c>
       <c r="C78">
-        <v>35.08124214334961</v>
+        <v>34.28889402937683</v>
       </c>
       <c r="D78">
-        <v>95.79524214334961</v>
+        <v>95.92689402937684</v>
       </c>
       <c r="E78">
-        <v>11.924</v>
+        <v>12.84800000000001</v>
       </c>
       <c r="F78">
-        <v>70.224</v>
+        <v>71.14800000000001</v>
       </c>
       <c r="G78">
         <v>9.51</v>
@@ -7677,28 +7677,28 @@
         <v>16.875</v>
       </c>
       <c r="M78">
-        <v>4.0589472</v>
+        <v>4.112354400000001</v>
       </c>
       <c r="N78">
-        <v>12.8160528</v>
+        <v>12.7626456</v>
       </c>
       <c r="O78">
-        <v>3.460334256</v>
+        <v>3.445914312</v>
       </c>
       <c r="P78">
-        <v>9.355718543999998</v>
+        <v>9.316731288</v>
       </c>
       <c r="Q78">
-        <v>9.355718543999998</v>
+        <v>9.316731288</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1690189652656528</v>
+        <v>0.1739395274329974</v>
       </c>
       <c r="T78">
-        <v>1.476131453378307</v>
+        <v>1.535078520234949</v>
       </c>
       <c r="U78">
         <v>0.0578</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.157482018982655</v>
+        <v>4.103488746008855</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07249547130958942</v>
+        <v>0.07235895095542214</v>
       </c>
       <c r="C79">
-        <v>34.28889402937683</v>
+        <v>33.49690827310043</v>
       </c>
       <c r="D79">
-        <v>95.92689402937684</v>
+        <v>96.05890827310043</v>
       </c>
       <c r="E79">
-        <v>12.84800000000001</v>
+        <v>13.772</v>
       </c>
       <c r="F79">
-        <v>71.14800000000001</v>
+        <v>72.072</v>
       </c>
       <c r="G79">
         <v>9.51</v>
@@ -7759,28 +7759,28 @@
         <v>16.875</v>
       </c>
       <c r="M79">
-        <v>4.112354400000001</v>
+        <v>4.165761600000001</v>
       </c>
       <c r="N79">
-        <v>12.7626456</v>
+        <v>12.7092384</v>
       </c>
       <c r="O79">
-        <v>3.445914312</v>
+        <v>3.431494368000001</v>
       </c>
       <c r="P79">
-        <v>9.316731288</v>
+        <v>9.277744031999999</v>
       </c>
       <c r="Q79">
-        <v>9.316731288</v>
+        <v>9.277744031999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1739395274329974</v>
+        <v>0.179307413433737</v>
       </c>
       <c r="T79">
-        <v>1.535078520234949</v>
+        <v>1.599384411351286</v>
       </c>
       <c r="U79">
         <v>0.0578</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.103488746008855</v>
+        <v>4.050879915931819</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07235895095542214</v>
+        <v>0.07424088060125487</v>
       </c>
       <c r="C80">
-        <v>33.49690827310043</v>
+        <v>30.78451807685406</v>
       </c>
       <c r="D80">
-        <v>96.05890827310043</v>
+        <v>94.27051807685406</v>
       </c>
       <c r="E80">
-        <v>13.772</v>
+        <v>14.69600000000001</v>
       </c>
       <c r="F80">
-        <v>72.072</v>
+        <v>72.99600000000001</v>
       </c>
       <c r="G80">
         <v>9.51</v>
@@ -7841,45 +7841,45 @@
         <v>16.875</v>
       </c>
       <c r="M80">
-        <v>4.165761600000001</v>
+        <v>4.474654800000001</v>
       </c>
       <c r="N80">
-        <v>12.7092384</v>
+        <v>12.4003452</v>
       </c>
       <c r="O80">
-        <v>3.431494368000001</v>
+        <v>3.348093204</v>
       </c>
       <c r="P80">
-        <v>9.277744031999999</v>
+        <v>9.052251995999999</v>
       </c>
       <c r="Q80">
-        <v>9.277744031999999</v>
+        <v>9.052251995999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.179307413433737</v>
+        <v>0.1851865266726423</v>
       </c>
       <c r="T80">
-        <v>1.599384411351286</v>
+        <v>1.669814673050132</v>
       </c>
       <c r="U80">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V80">
         <v>0.27</v>
       </c>
       <c r="W80">
-        <v>0.042194</v>
+        <v>0.044749</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y80">
-        <v>4.050879915931819</v>
+        <v>3.77124063290871</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07424088060125487</v>
+        <v>0.07412991024708759</v>
       </c>
       <c r="C81">
-        <v>30.78451807685406</v>
+        <v>29.96412318109819</v>
       </c>
       <c r="D81">
-        <v>94.27051807685406</v>
+        <v>94.37412318109818</v>
       </c>
       <c r="E81">
-        <v>14.69600000000001</v>
+        <v>15.62</v>
       </c>
       <c r="F81">
-        <v>72.99600000000001</v>
+        <v>73.92</v>
       </c>
       <c r="G81">
         <v>9.51</v>
@@ -7923,28 +7923,28 @@
         <v>16.875</v>
       </c>
       <c r="M81">
-        <v>4.474654800000001</v>
+        <v>4.531296</v>
       </c>
       <c r="N81">
-        <v>12.4003452</v>
+        <v>12.343704</v>
       </c>
       <c r="O81">
-        <v>3.348093204</v>
+        <v>3.33280008</v>
       </c>
       <c r="P81">
-        <v>9.052251995999999</v>
+        <v>9.010903919999999</v>
       </c>
       <c r="Q81">
-        <v>9.052251995999999</v>
+        <v>9.010903919999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1851865266726423</v>
+        <v>0.1916535512354381</v>
       </c>
       <c r="T81">
-        <v>1.669814673050132</v>
+        <v>1.747287960918862</v>
       </c>
       <c r="U81">
         <v>0.0613</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.77124063290871</v>
+        <v>3.724100124997352</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.07412991024708759</v>
+        <v>0.07401893989292033</v>
       </c>
       <c r="C82">
-        <v>29.96412318109819</v>
+        <v>29.14395626388139</v>
       </c>
       <c r="D82">
-        <v>94.37412318109818</v>
+        <v>94.4779562638814</v>
       </c>
       <c r="E82">
-        <v>15.62</v>
+        <v>16.544</v>
       </c>
       <c r="F82">
-        <v>73.92</v>
+        <v>74.84400000000001</v>
       </c>
       <c r="G82">
         <v>9.51</v>
@@ -8005,28 +8005,28 @@
         <v>16.875</v>
       </c>
       <c r="M82">
-        <v>4.531296</v>
+        <v>4.587937200000001</v>
       </c>
       <c r="N82">
-        <v>12.343704</v>
+        <v>12.2870628</v>
       </c>
       <c r="O82">
-        <v>3.33280008</v>
+        <v>3.317506956</v>
       </c>
       <c r="P82">
-        <v>9.010903919999999</v>
+        <v>8.969555843999999</v>
       </c>
       <c r="Q82">
-        <v>9.010903919999999</v>
+        <v>8.969555843999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1916535512354381</v>
+        <v>0.1988013152258966</v>
       </c>
       <c r="T82">
-        <v>1.747287960918862</v>
+        <v>1.832916331721142</v>
       </c>
       <c r="U82">
         <v>0.0613</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.724100124997352</v>
+        <v>3.678123580244297</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07401893989292033</v>
+        <v>0.07390796953875307</v>
       </c>
       <c r="C83">
-        <v>29.14395626388139</v>
+        <v>28.32401807851781</v>
       </c>
       <c r="D83">
-        <v>94.4779562638814</v>
+        <v>94.58201807851782</v>
       </c>
       <c r="E83">
-        <v>16.544</v>
+        <v>17.46800000000001</v>
       </c>
       <c r="F83">
-        <v>74.84400000000001</v>
+        <v>75.76800000000001</v>
       </c>
       <c r="G83">
         <v>9.51</v>
@@ -8087,28 +8087,28 @@
         <v>16.875</v>
       </c>
       <c r="M83">
-        <v>4.587937200000001</v>
+        <v>4.644578400000001</v>
       </c>
       <c r="N83">
-        <v>12.2870628</v>
+        <v>12.2304216</v>
       </c>
       <c r="O83">
-        <v>3.317506956</v>
+        <v>3.302213832</v>
       </c>
       <c r="P83">
-        <v>8.969555843999999</v>
+        <v>8.928207768</v>
       </c>
       <c r="Q83">
-        <v>8.969555843999999</v>
+        <v>8.928207768</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1988013152258966</v>
+        <v>0.2067432752152949</v>
       </c>
       <c r="T83">
-        <v>1.832916331721142</v>
+        <v>1.928058965945898</v>
       </c>
       <c r="U83">
         <v>0.0613</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.678123580244297</v>
+        <v>3.633268414631562</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07390796953875307</v>
+        <v>0.07379699918458582</v>
       </c>
       <c r="C84">
-        <v>28.32401807851781</v>
+        <v>27.50430938164425</v>
       </c>
       <c r="D84">
-        <v>94.58201807851782</v>
+        <v>94.68630938164425</v>
       </c>
       <c r="E84">
-        <v>17.46800000000001</v>
+        <v>18.392</v>
       </c>
       <c r="F84">
-        <v>75.76800000000001</v>
+        <v>76.69200000000001</v>
       </c>
       <c r="G84">
         <v>9.51</v>
@@ -8169,28 +8169,28 @@
         <v>16.875</v>
       </c>
       <c r="M84">
-        <v>4.644578400000001</v>
+        <v>4.701219600000001</v>
       </c>
       <c r="N84">
-        <v>12.2304216</v>
+        <v>12.1737804</v>
       </c>
       <c r="O84">
-        <v>3.302213832</v>
+        <v>3.286920708</v>
       </c>
       <c r="P84">
-        <v>8.928207768</v>
+        <v>8.886859691999998</v>
       </c>
       <c r="Q84">
-        <v>8.928207768</v>
+        <v>8.886859691999998</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2067432752152949</v>
+        <v>0.2156195834387402</v>
       </c>
       <c r="T84">
-        <v>1.928058965945898</v>
+        <v>2.03439485125592</v>
       </c>
       <c r="U84">
         <v>0.0613</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.633268414631562</v>
+        <v>3.589494096382989</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07379699918458582</v>
+        <v>0.07368602883041855</v>
       </c>
       <c r="C85">
-        <v>27.50430938164425</v>
+        <v>26.68483093323832</v>
       </c>
       <c r="D85">
-        <v>94.68630938164425</v>
+        <v>94.79083093323833</v>
       </c>
       <c r="E85">
-        <v>18.392</v>
+        <v>19.31600000000001</v>
       </c>
       <c r="F85">
-        <v>76.69200000000001</v>
+        <v>77.61600000000001</v>
       </c>
       <c r="G85">
         <v>9.51</v>
@@ -8251,28 +8251,28 @@
         <v>16.875</v>
       </c>
       <c r="M85">
-        <v>4.701219600000001</v>
+        <v>4.7578608</v>
       </c>
       <c r="N85">
-        <v>12.1737804</v>
+        <v>12.1171392</v>
       </c>
       <c r="O85">
-        <v>3.286920708</v>
+        <v>3.271627584</v>
       </c>
       <c r="P85">
-        <v>8.886859691999998</v>
+        <v>8.845511616</v>
       </c>
       <c r="Q85">
-        <v>8.886859691999998</v>
+        <v>8.845511616</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2156195834387402</v>
+        <v>0.225605430190116</v>
       </c>
       <c r="T85">
-        <v>2.03439485125592</v>
+        <v>2.154022722229695</v>
       </c>
       <c r="U85">
         <v>0.0613</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.589494096382989</v>
+        <v>3.546762023807001</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07368602883041855</v>
+        <v>0.07357505847625129</v>
       </c>
       <c r="C86">
-        <v>26.68483093323833</v>
+        <v>25.86558349663707</v>
       </c>
       <c r="D86">
-        <v>94.79083093323833</v>
+        <v>94.89558349663707</v>
       </c>
       <c r="E86">
-        <v>19.316</v>
+        <v>20.24</v>
       </c>
       <c r="F86">
-        <v>77.616</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="G86">
         <v>9.51</v>
@@ -8333,28 +8333,28 @@
         <v>16.875</v>
       </c>
       <c r="M86">
-        <v>4.7578608</v>
+        <v>4.814502</v>
       </c>
       <c r="N86">
-        <v>12.1171392</v>
+        <v>12.060498</v>
       </c>
       <c r="O86">
-        <v>3.271627584</v>
+        <v>3.25633446</v>
       </c>
       <c r="P86">
-        <v>8.845511616</v>
+        <v>8.804163539999999</v>
       </c>
       <c r="Q86">
-        <v>8.845511616</v>
+        <v>8.804163539999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2256054301901159</v>
+        <v>0.2369227231750085</v>
       </c>
       <c r="T86">
-        <v>2.154022722229693</v>
+        <v>2.28960097599997</v>
       </c>
       <c r="U86">
         <v>0.0613</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.546762023807001</v>
+        <v>3.505035411762213</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.07357505847625129</v>
+        <v>0.07522192812208403</v>
       </c>
       <c r="C87">
-        <v>25.86558349663707</v>
+        <v>23.41038385974869</v>
       </c>
       <c r="D87">
-        <v>94.89558349663707</v>
+        <v>93.36438385974868</v>
       </c>
       <c r="E87">
-        <v>20.24</v>
+        <v>21.16399999999999</v>
       </c>
       <c r="F87">
-        <v>78.54000000000001</v>
+        <v>79.464</v>
       </c>
       <c r="G87">
         <v>9.51</v>
@@ -8415,45 +8415,45 @@
         <v>16.875</v>
       </c>
       <c r="M87">
-        <v>4.814502</v>
+        <v>5.0936424</v>
       </c>
       <c r="N87">
-        <v>12.060498</v>
+        <v>11.7813576</v>
       </c>
       <c r="O87">
-        <v>3.25633446</v>
+        <v>3.180966552</v>
       </c>
       <c r="P87">
-        <v>8.804163539999999</v>
+        <v>8.600391047999999</v>
       </c>
       <c r="Q87">
-        <v>8.804163539999999</v>
+        <v>8.600391047999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2369227231750085</v>
+        <v>0.2498567723006001</v>
       </c>
       <c r="T87">
-        <v>2.28960097599997</v>
+        <v>2.44454755173743</v>
       </c>
       <c r="U87">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V87">
         <v>0.27</v>
       </c>
       <c r="W87">
-        <v>0.044749</v>
+        <v>0.046793</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y87">
-        <v>3.505035411762213</v>
+        <v>3.312953418166929</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.07522192812208403</v>
+        <v>0.07513139776791675</v>
       </c>
       <c r="C88">
-        <v>23.41038385974869</v>
+        <v>22.56927105315701</v>
       </c>
       <c r="D88">
-        <v>93.36438385974868</v>
+        <v>93.44727105315701</v>
       </c>
       <c r="E88">
-        <v>21.16399999999999</v>
+        <v>22.088</v>
       </c>
       <c r="F88">
-        <v>79.464</v>
+        <v>80.38800000000001</v>
       </c>
       <c r="G88">
         <v>9.51</v>
@@ -8497,28 +8497,28 @@
         <v>16.875</v>
       </c>
       <c r="M88">
-        <v>5.0936424</v>
+        <v>5.152870800000001</v>
       </c>
       <c r="N88">
-        <v>11.7813576</v>
+        <v>11.7221292</v>
       </c>
       <c r="O88">
-        <v>3.180966552</v>
+        <v>3.164974884</v>
       </c>
       <c r="P88">
-        <v>8.600391047999999</v>
+        <v>8.557154315999998</v>
       </c>
       <c r="Q88">
-        <v>8.600391047999999</v>
+        <v>8.557154315999998</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2498567723006001</v>
+        <v>0.2647806751378211</v>
       </c>
       <c r="T88">
-        <v>2.44454755173743</v>
+        <v>2.62333206220373</v>
       </c>
       <c r="U88">
         <v>0.0641</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.312953418166929</v>
+        <v>3.274873493820182</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.07513139776791675</v>
+        <v>0.07504086741374948</v>
       </c>
       <c r="C89">
-        <v>22.56927105315701</v>
+        <v>21.72830554880801</v>
       </c>
       <c r="D89">
-        <v>93.44727105315701</v>
+        <v>93.53030554880802</v>
       </c>
       <c r="E89">
-        <v>22.088</v>
+        <v>23.01200000000001</v>
       </c>
       <c r="F89">
-        <v>80.38800000000001</v>
+        <v>81.31200000000001</v>
       </c>
       <c r="G89">
         <v>9.51</v>
@@ -8579,28 +8579,28 @@
         <v>16.875</v>
       </c>
       <c r="M89">
-        <v>5.152870800000001</v>
+        <v>5.212099200000001</v>
       </c>
       <c r="N89">
-        <v>11.7221292</v>
+        <v>11.6629008</v>
       </c>
       <c r="O89">
-        <v>3.164974884</v>
+        <v>3.148983216</v>
       </c>
       <c r="P89">
-        <v>8.557154315999998</v>
+        <v>8.513917584</v>
       </c>
       <c r="Q89">
-        <v>8.557154315999998</v>
+        <v>8.513917584</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2647806751378211</v>
+        <v>0.282191895114579</v>
       </c>
       <c r="T89">
-        <v>2.62333206220373</v>
+        <v>2.83191399108108</v>
       </c>
       <c r="U89">
         <v>0.0641</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.274873493820182</v>
+        <v>3.237659022299499</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.07504086741374948</v>
+        <v>0.07495033705958221</v>
       </c>
       <c r="C90">
-        <v>21.72830554880801</v>
+        <v>20.88748773971628</v>
       </c>
       <c r="D90">
-        <v>93.53030554880802</v>
+        <v>93.61348773971628</v>
       </c>
       <c r="E90">
-        <v>23.01200000000001</v>
+        <v>23.936</v>
       </c>
       <c r="F90">
-        <v>81.31200000000001</v>
+        <v>82.236</v>
       </c>
       <c r="G90">
         <v>9.51</v>
@@ -8661,28 +8661,28 @@
         <v>16.875</v>
       </c>
       <c r="M90">
-        <v>5.212099200000001</v>
+        <v>5.2713276</v>
       </c>
       <c r="N90">
-        <v>11.6629008</v>
+        <v>11.6036724</v>
       </c>
       <c r="O90">
-        <v>3.148983216</v>
+        <v>3.132991548000001</v>
       </c>
       <c r="P90">
-        <v>8.513917584</v>
+        <v>8.470680852000001</v>
       </c>
       <c r="Q90">
-        <v>8.513917584</v>
+        <v>8.470680852000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.282191895114579</v>
+        <v>0.3027687914507474</v>
       </c>
       <c r="T90">
-        <v>2.83191399108108</v>
+        <v>3.078419907027039</v>
       </c>
       <c r="U90">
         <v>0.0641</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.237659022299499</v>
+        <v>3.201280831037707</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.07495033705958221</v>
+        <v>0.07485980670541495</v>
       </c>
       <c r="C91">
-        <v>20.88748773971628</v>
+        <v>20.04681802029569</v>
       </c>
       <c r="D91">
-        <v>93.61348773971628</v>
+        <v>93.69681802029569</v>
       </c>
       <c r="E91">
-        <v>23.936</v>
+        <v>24.86000000000001</v>
       </c>
       <c r="F91">
-        <v>82.236</v>
+        <v>83.16000000000001</v>
       </c>
       <c r="G91">
         <v>9.51</v>
@@ -8743,28 +8743,28 @@
         <v>16.875</v>
       </c>
       <c r="M91">
-        <v>5.2713276</v>
+        <v>5.330556000000001</v>
       </c>
       <c r="N91">
-        <v>11.6036724</v>
+        <v>11.544444</v>
       </c>
       <c r="O91">
-        <v>3.132991548000001</v>
+        <v>3.11699988</v>
       </c>
       <c r="P91">
-        <v>8.470680852000001</v>
+        <v>8.427444119999999</v>
       </c>
       <c r="Q91">
-        <v>8.470680852000001</v>
+        <v>8.427444119999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3027687914507474</v>
+        <v>0.3274610670541496</v>
       </c>
       <c r="T91">
-        <v>3.078419907027039</v>
+        <v>3.37422700616219</v>
       </c>
       <c r="U91">
         <v>0.0641</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.201280831037707</v>
+        <v>3.165711044026176</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.07485980670541495</v>
+        <v>0.07476927635124768</v>
       </c>
       <c r="C92">
-        <v>20.04681802029569</v>
+        <v>19.20629678636578</v>
       </c>
       <c r="D92">
-        <v>93.69681802029569</v>
+        <v>93.78029678636578</v>
       </c>
       <c r="E92">
-        <v>24.86000000000001</v>
+        <v>25.784</v>
       </c>
       <c r="F92">
-        <v>83.16000000000001</v>
+        <v>84.084</v>
       </c>
       <c r="G92">
         <v>9.51</v>
@@ -8825,28 +8825,28 @@
         <v>16.875</v>
       </c>
       <c r="M92">
-        <v>5.330556000000001</v>
+        <v>5.389784400000001</v>
       </c>
       <c r="N92">
-        <v>11.544444</v>
+        <v>11.4852156</v>
       </c>
       <c r="O92">
-        <v>3.11699988</v>
+        <v>3.101008212</v>
       </c>
       <c r="P92">
-        <v>8.427444119999999</v>
+        <v>8.384207388</v>
       </c>
       <c r="Q92">
-        <v>8.427444119999999</v>
+        <v>8.384207388</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3274610670541496</v>
+        <v>0.3576405150138632</v>
       </c>
       <c r="T92">
-        <v>3.37422700616219</v>
+        <v>3.735769016216263</v>
       </c>
       <c r="U92">
         <v>0.0641</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.165711044026176</v>
+        <v>3.130923010575339</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.07476927635124768</v>
+        <v>0.07467874599708041</v>
       </c>
       <c r="C93">
-        <v>19.20629678636578</v>
+        <v>18.36592443515792</v>
       </c>
       <c r="D93">
-        <v>93.78029678636578</v>
+        <v>93.86392443515793</v>
       </c>
       <c r="E93">
-        <v>25.784</v>
+        <v>26.70800000000001</v>
       </c>
       <c r="F93">
-        <v>84.084</v>
+        <v>85.00800000000001</v>
       </c>
       <c r="G93">
         <v>9.51</v>
@@ -8907,28 +8907,28 @@
         <v>16.875</v>
       </c>
       <c r="M93">
-        <v>5.389784400000001</v>
+        <v>5.449012800000001</v>
       </c>
       <c r="N93">
-        <v>11.4852156</v>
+        <v>11.4259872</v>
       </c>
       <c r="O93">
-        <v>3.101008212</v>
+        <v>3.085016544</v>
       </c>
       <c r="P93">
-        <v>8.384207388</v>
+        <v>8.340970655999998</v>
       </c>
       <c r="Q93">
-        <v>8.384207388</v>
+        <v>8.340970655999998</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3576405150138632</v>
+        <v>0.3953648249635054</v>
       </c>
       <c r="T93">
-        <v>3.735769016216263</v>
+        <v>4.187696528783855</v>
       </c>
       <c r="U93">
         <v>0.0641</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.130923010575339</v>
+        <v>3.096891238721259</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.07467874599708041</v>
+        <v>0.07458821564291315</v>
       </c>
       <c r="C94">
-        <v>18.36592443515792</v>
+        <v>17.52570136532167</v>
       </c>
       <c r="D94">
-        <v>93.86392443515793</v>
+        <v>93.94770136532168</v>
       </c>
       <c r="E94">
-        <v>26.70800000000001</v>
+        <v>27.63200000000001</v>
       </c>
       <c r="F94">
-        <v>85.00800000000001</v>
+        <v>85.93200000000002</v>
       </c>
       <c r="G94">
         <v>9.51</v>
@@ -8989,28 +8989,28 @@
         <v>16.875</v>
       </c>
       <c r="M94">
-        <v>5.449012800000001</v>
+        <v>5.508241200000001</v>
       </c>
       <c r="N94">
-        <v>11.4259872</v>
+        <v>11.3667588</v>
       </c>
       <c r="O94">
-        <v>3.085016544</v>
+        <v>3.069024876</v>
       </c>
       <c r="P94">
-        <v>8.340970655999998</v>
+        <v>8.297733923999999</v>
       </c>
       <c r="Q94">
-        <v>8.340970655999998</v>
+        <v>8.297733923999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3953648249635054</v>
+        <v>0.4438675091844738</v>
       </c>
       <c r="T94">
-        <v>4.187696528783855</v>
+        <v>4.76874618779933</v>
       </c>
       <c r="U94">
         <v>0.0641</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.096891238721259</v>
+        <v>3.063591332928557</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.07458821564291315</v>
+        <v>0.07449768528874588</v>
       </c>
       <c r="C95">
-        <v>17.52570136532167</v>
+        <v>16.68562797693113</v>
       </c>
       <c r="D95">
-        <v>93.94770136532168</v>
+        <v>94.03162797693113</v>
       </c>
       <c r="E95">
-        <v>27.63200000000001</v>
+        <v>28.556</v>
       </c>
       <c r="F95">
-        <v>85.93200000000002</v>
+        <v>86.85600000000001</v>
       </c>
       <c r="G95">
         <v>9.51</v>
@@ -9071,28 +9071,28 @@
         <v>16.875</v>
       </c>
       <c r="M95">
-        <v>5.508241200000001</v>
+        <v>5.567469600000001</v>
       </c>
       <c r="N95">
-        <v>11.3667588</v>
+        <v>11.3075304</v>
       </c>
       <c r="O95">
-        <v>3.069024876</v>
+        <v>3.053033208</v>
       </c>
       <c r="P95">
-        <v>8.297733923999999</v>
+        <v>8.254497191999999</v>
       </c>
       <c r="Q95">
-        <v>8.297733923999999</v>
+        <v>8.254497191999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4438675091844738</v>
+        <v>0.5085377548124318</v>
       </c>
       <c r="T95">
-        <v>4.76874618779933</v>
+        <v>5.543479066486631</v>
       </c>
       <c r="U95">
         <v>0.0641</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.063591332928557</v>
+        <v>3.030999935769743</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.07449768528874588</v>
+        <v>0.07981645493457862</v>
       </c>
       <c r="C96">
-        <v>16.68562797693113</v>
+        <v>11.07253582116383</v>
       </c>
       <c r="D96">
-        <v>94.03162797693113</v>
+        <v>89.34253582116384</v>
       </c>
       <c r="E96">
-        <v>28.556</v>
+        <v>29.48000000000001</v>
       </c>
       <c r="F96">
-        <v>86.85600000000001</v>
+        <v>87.78000000000002</v>
       </c>
       <c r="G96">
         <v>9.51</v>
@@ -9153,45 +9153,45 @@
         <v>16.875</v>
       </c>
       <c r="M96">
-        <v>5.567469600000001</v>
+        <v>6.311382000000002</v>
       </c>
       <c r="N96">
-        <v>11.3075304</v>
+        <v>10.563618</v>
       </c>
       <c r="O96">
-        <v>3.053033208</v>
+        <v>2.85217686</v>
       </c>
       <c r="P96">
-        <v>8.254497191999999</v>
+        <v>7.711441139999998</v>
       </c>
       <c r="Q96">
-        <v>8.254497191999999</v>
+        <v>7.711441139999998</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5085377548124318</v>
+        <v>0.5990760986915731</v>
       </c>
       <c r="T96">
-        <v>5.543479066486631</v>
+        <v>6.628105096648853</v>
       </c>
       <c r="U96">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V96">
         <v>0.27</v>
       </c>
       <c r="W96">
-        <v>0.046793</v>
+        <v>0.05248700000000001</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y96">
-        <v>3.030999935769743</v>
+        <v>2.673740870066175</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.07981645493457862</v>
+        <v>0.07978286458041135</v>
       </c>
       <c r="C97">
-        <v>11.07253582116383</v>
+        <v>10.17668160089123</v>
       </c>
       <c r="D97">
-        <v>89.34253582116384</v>
+        <v>89.37068160089123</v>
       </c>
       <c r="E97">
-        <v>29.48000000000001</v>
+        <v>30.404</v>
       </c>
       <c r="F97">
-        <v>87.78000000000002</v>
+        <v>88.70400000000001</v>
       </c>
       <c r="G97">
         <v>9.51</v>
@@ -9235,28 +9235,28 @@
         <v>16.875</v>
       </c>
       <c r="M97">
-        <v>6.311382000000002</v>
+        <v>6.377817600000001</v>
       </c>
       <c r="N97">
-        <v>10.563618</v>
+        <v>10.4971824</v>
       </c>
       <c r="O97">
-        <v>2.85217686</v>
+        <v>2.834239248</v>
       </c>
       <c r="P97">
-        <v>7.711441139999998</v>
+        <v>7.662943152</v>
       </c>
       <c r="Q97">
-        <v>7.711441139999998</v>
+        <v>7.662943152</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5990760986915731</v>
+        <v>0.7348836145102849</v>
       </c>
       <c r="T97">
-        <v>6.628105096648853</v>
+        <v>8.255044141892187</v>
       </c>
       <c r="U97">
         <v>0.07190000000000001</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.673740870066175</v>
+        <v>2.645889402669653</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.07978286458041135</v>
+        <v>0.07974927422624409</v>
       </c>
       <c r="C98">
-        <v>10.17668160089123</v>
+        <v>9.280845119863471</v>
       </c>
       <c r="D98">
-        <v>89.37068160089123</v>
+        <v>89.39884511986347</v>
       </c>
       <c r="E98">
-        <v>30.404</v>
+        <v>31.328</v>
       </c>
       <c r="F98">
-        <v>88.70400000000001</v>
+        <v>89.628</v>
       </c>
       <c r="G98">
         <v>9.51</v>
@@ -9317,28 +9317,28 @@
         <v>16.875</v>
       </c>
       <c r="M98">
-        <v>6.377817600000001</v>
+        <v>6.4442532</v>
       </c>
       <c r="N98">
-        <v>10.4971824</v>
+        <v>10.4307468</v>
       </c>
       <c r="O98">
-        <v>2.834239248</v>
+        <v>2.816301636</v>
       </c>
       <c r="P98">
-        <v>7.662943152</v>
+        <v>7.614445163999999</v>
       </c>
       <c r="Q98">
-        <v>7.662943152</v>
+        <v>7.614445163999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7348836145102832</v>
+        <v>0.9612294742081354</v>
       </c>
       <c r="T98">
-        <v>8.255044141892165</v>
+        <v>10.96660921729771</v>
       </c>
       <c r="U98">
         <v>0.07190000000000001</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.645889402669653</v>
+        <v>2.618612192332852</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.07974927422624409</v>
+        <v>0.07971568387207682</v>
       </c>
       <c r="C99">
-        <v>9.280845119863471</v>
+        <v>8.385026394856425</v>
       </c>
       <c r="D99">
-        <v>89.39884511986347</v>
+        <v>89.42702639485643</v>
       </c>
       <c r="E99">
-        <v>31.328</v>
+        <v>32.252</v>
       </c>
       <c r="F99">
-        <v>89.628</v>
+        <v>90.55200000000001</v>
       </c>
       <c r="G99">
         <v>9.51</v>
@@ -9399,28 +9399,28 @@
         <v>16.875</v>
       </c>
       <c r="M99">
-        <v>6.4442532</v>
+        <v>6.510688800000001</v>
       </c>
       <c r="N99">
-        <v>10.4307468</v>
+        <v>10.3643112</v>
       </c>
       <c r="O99">
-        <v>2.816301636</v>
+        <v>2.798364024</v>
       </c>
       <c r="P99">
-        <v>7.614445163999999</v>
+        <v>7.565947176</v>
       </c>
       <c r="Q99">
-        <v>7.614445163999999</v>
+        <v>7.565947176</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9612294742081354</v>
+        <v>1.41392119360384</v>
       </c>
       <c r="T99">
-        <v>10.96660921729771</v>
+        <v>16.3897393681088</v>
       </c>
       <c r="U99">
         <v>0.07190000000000001</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.618612192332852</v>
+        <v>2.591891659758027</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.07971568387207682</v>
+        <v>0.07968209351790956</v>
       </c>
       <c r="C100">
-        <v>8.385026394856425</v>
+        <v>7.489225442667134</v>
       </c>
       <c r="D100">
-        <v>89.42702639485643</v>
+        <v>89.45522544266713</v>
       </c>
       <c r="E100">
-        <v>32.252</v>
+        <v>33.17599999999999</v>
       </c>
       <c r="F100">
-        <v>90.55200000000001</v>
+        <v>91.476</v>
       </c>
       <c r="G100">
         <v>9.51</v>
@@ -9481,28 +9481,28 @@
         <v>16.875</v>
       </c>
       <c r="M100">
-        <v>6.510688800000001</v>
+        <v>6.577124400000001</v>
       </c>
       <c r="N100">
-        <v>10.3643112</v>
+        <v>10.2978756</v>
       </c>
       <c r="O100">
-        <v>2.798364024</v>
+        <v>2.780426412</v>
       </c>
       <c r="P100">
-        <v>7.565947176</v>
+        <v>7.517449187999999</v>
       </c>
       <c r="Q100">
-        <v>7.565947176</v>
+        <v>7.517449187999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.41392119360384</v>
+        <v>2.771996351790953</v>
       </c>
       <c r="T100">
-        <v>16.3897393681088</v>
+        <v>32.65912982054206</v>
       </c>
       <c r="U100">
         <v>0.07190000000000001</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.591891659758027</v>
+        <v>2.565710935922088</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.07968209351790956</v>
-      </c>
-      <c r="C101">
-        <v>7.489225442667134</v>
-      </c>
-      <c r="D101">
-        <v>89.45522544266713</v>
-      </c>
-      <c r="E101">
-        <v>33.17599999999999</v>
-      </c>
-      <c r="F101">
-        <v>91.476</v>
-      </c>
-      <c r="G101">
-        <v>9.51</v>
-      </c>
-      <c r="H101">
-        <v>34.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>16.875</v>
-      </c>
-      <c r="K101">
-        <v>0</v>
-      </c>
-      <c r="L101">
-        <v>16.875</v>
-      </c>
-      <c r="M101">
-        <v>6.577124400000001</v>
-      </c>
-      <c r="N101">
-        <v>10.2978756</v>
-      </c>
-      <c r="O101">
-        <v>2.780426412</v>
-      </c>
-      <c r="P101">
-        <v>7.517449187999999</v>
-      </c>
-      <c r="Q101">
-        <v>7.517449187999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.771996351790953</v>
-      </c>
-      <c r="T101">
-        <v>32.65912982054206</v>
-      </c>
-      <c r="U101">
-        <v>0.07190000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.27</v>
-      </c>
-      <c r="W101">
-        <v>0.05248700000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B1/B+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.565710935922088</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
